--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1389,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ13">
         <v>1.55</v>
@@ -4610,7 +4610,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ33">
         <v>1.3</v>
@@ -8318,7 +8318,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR34">
         <v>1.12</v>
@@ -10169,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ43">
         <v>0.64</v>
@@ -10790,7 +10790,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ46">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR46">
         <v>1.3</v>
@@ -14086,7 +14086,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ62">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR62">
         <v>1.68</v>
@@ -17173,7 +17173,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ77">
         <v>1.7</v>
@@ -19648,7 +19648,7 @@
         <v>2</v>
       </c>
       <c r="AQ89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR89">
         <v>1.66</v>
@@ -20263,7 +20263,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -22326,7 +22326,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ102">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR102">
         <v>1.75</v>
@@ -25416,7 +25416,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -27679,7 +27679,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ128">
         <v>1.73</v>
@@ -29124,7 +29124,7 @@
         <v>1</v>
       </c>
       <c r="AQ135">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR135">
         <v>1.75</v>
@@ -30563,7 +30563,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ142">
         <v>1.11</v>
@@ -35098,7 +35098,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ164">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35507,7 +35507,7 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ166">
         <v>2.2</v>
@@ -38803,7 +38803,7 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ182">
         <v>1.6</v>
@@ -40454,7 +40454,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR190">
         <v>1.73</v>
@@ -43414,6 +43414,212 @@
       </c>
       <c r="BP204">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7465618</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45669.34375</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>81</v>
+      </c>
+      <c r="H205" t="s">
+        <v>79</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
+        <v>144</v>
+      </c>
+      <c r="P205" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q205">
+        <v>1.95</v>
+      </c>
+      <c r="R205">
+        <v>2.63</v>
+      </c>
+      <c r="S205">
+        <v>5.5</v>
+      </c>
+      <c r="T205">
+        <v>1.25</v>
+      </c>
+      <c r="U205">
+        <v>3.75</v>
+      </c>
+      <c r="V205">
+        <v>2.2</v>
+      </c>
+      <c r="W205">
+        <v>1.62</v>
+      </c>
+      <c r="X205">
+        <v>5</v>
+      </c>
+      <c r="Y205">
+        <v>1.17</v>
+      </c>
+      <c r="Z205">
+        <v>1.45</v>
+      </c>
+      <c r="AA205">
+        <v>4.5</v>
+      </c>
+      <c r="AB205">
+        <v>6.5</v>
+      </c>
+      <c r="AC205">
+        <v>1.02</v>
+      </c>
+      <c r="AD205">
+        <v>17</v>
+      </c>
+      <c r="AE205">
+        <v>1.12</v>
+      </c>
+      <c r="AF205">
+        <v>6</v>
+      </c>
+      <c r="AG205">
+        <v>1.44</v>
+      </c>
+      <c r="AH205">
+        <v>2.7</v>
+      </c>
+      <c r="AI205">
+        <v>1.57</v>
+      </c>
+      <c r="AJ205">
+        <v>2.25</v>
+      </c>
+      <c r="AK205">
+        <v>1.12</v>
+      </c>
+      <c r="AL205">
+        <v>1.14</v>
+      </c>
+      <c r="AM205">
+        <v>2.7</v>
+      </c>
+      <c r="AN205">
+        <v>1.56</v>
+      </c>
+      <c r="AO205">
+        <v>1.3</v>
+      </c>
+      <c r="AP205">
+        <v>1.7</v>
+      </c>
+      <c r="AQ205">
+        <v>1.18</v>
+      </c>
+      <c r="AR205">
+        <v>1.65</v>
+      </c>
+      <c r="AS205">
+        <v>1.31</v>
+      </c>
+      <c r="AT205">
+        <v>2.96</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>2</v>
+      </c>
+      <c r="AW205">
+        <v>18</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>33</v>
+      </c>
+      <c r="AZ205">
+        <v>10</v>
+      </c>
+      <c r="BA205">
+        <v>12</v>
+      </c>
+      <c r="BB205">
+        <v>1</v>
+      </c>
+      <c r="BC205">
+        <v>13</v>
+      </c>
+      <c r="BD205">
+        <v>1.43</v>
+      </c>
+      <c r="BE205">
+        <v>6.75</v>
+      </c>
+      <c r="BF205">
+        <v>3.15</v>
+      </c>
+      <c r="BG205">
+        <v>1.29</v>
+      </c>
+      <c r="BH205">
+        <v>3.15</v>
+      </c>
+      <c r="BI205">
+        <v>1.5</v>
+      </c>
+      <c r="BJ205">
+        <v>2.35</v>
+      </c>
+      <c r="BK205">
+        <v>1.83</v>
+      </c>
+      <c r="BL205">
+        <v>1.85</v>
+      </c>
+      <c r="BM205">
+        <v>2.3</v>
+      </c>
+      <c r="BN205">
+        <v>1.54</v>
+      </c>
+      <c r="BO205">
+        <v>2.95</v>
+      </c>
+      <c r="BP205">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1029,6 +1029,9 @@
   <si>
     <t>['22', '41', '82']</t>
   </si>
+  <si>
+    <t>['10', '13', '57', '75']</t>
+  </si>
 </sst>
 </file>
 
@@ -1389,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2753,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ7">
         <v>1.09</v>
@@ -2962,7 +2965,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ8">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -7079,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28">
         <v>1.55</v>
@@ -7903,7 +7906,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ32">
         <v>1.55</v>
@@ -8730,7 +8733,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -12644,7 +12647,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ55">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -15319,7 +15322,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ68">
         <v>0.9</v>
@@ -16146,7 +16149,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ72">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -18409,7 +18412,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ83">
         <v>1.73</v>
@@ -20472,7 +20475,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ93">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -25413,7 +25416,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ117">
         <v>1.18</v>
@@ -26652,7 +26655,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ123">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27267,7 +27270,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ126">
         <v>0.5</v>
@@ -30566,7 +30569,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ142">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -31593,7 +31596,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ147">
         <v>2.2</v>
@@ -35713,7 +35716,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ167">
         <v>1.6</v>
@@ -36128,7 +36131,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ169">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -39424,7 +39427,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ185">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -40657,7 +40660,7 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ191">
         <v>0.5600000000000001</v>
@@ -42941,19 +42944,19 @@
         <v>3</v>
       </c>
       <c r="AV202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW202">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX202">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY202">
         <v>9</v>
       </c>
       <c r="AZ202">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA202">
         <v>2</v>
@@ -43147,19 +43150,19 @@
         <v>7</v>
       </c>
       <c r="AV203">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW203">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX203">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AY203">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ203">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA203">
         <v>6</v>
@@ -43350,22 +43353,22 @@
         <v>3.11</v>
       </c>
       <c r="AU204">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV204">
         <v>2</v>
       </c>
       <c r="AW204">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX204">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY204">
         <v>9</v>
       </c>
       <c r="AZ204">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA204">
         <v>6</v>
@@ -43556,22 +43559,22 @@
         <v>2.96</v>
       </c>
       <c r="AU205">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV205">
         <v>2</v>
       </c>
       <c r="AW205">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AX205">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY205">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AZ205">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA205">
         <v>12</v>
@@ -43620,6 +43623,212 @@
       </c>
       <c r="BP205">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7465621</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45669.53125</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>75</v>
+      </c>
+      <c r="H206" t="s">
+        <v>80</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>2</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>4</v>
+      </c>
+      <c r="N206">
+        <v>5</v>
+      </c>
+      <c r="O206" t="s">
+        <v>156</v>
+      </c>
+      <c r="P206" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q206">
+        <v>2.4</v>
+      </c>
+      <c r="R206">
+        <v>2.38</v>
+      </c>
+      <c r="S206">
+        <v>4</v>
+      </c>
+      <c r="T206">
+        <v>1.3</v>
+      </c>
+      <c r="U206">
+        <v>3.4</v>
+      </c>
+      <c r="V206">
+        <v>2.5</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>6</v>
+      </c>
+      <c r="Y206">
+        <v>1.13</v>
+      </c>
+      <c r="Z206">
+        <v>1.83</v>
+      </c>
+      <c r="AA206">
+        <v>3.9</v>
+      </c>
+      <c r="AB206">
+        <v>3.75</v>
+      </c>
+      <c r="AC206">
+        <v>1.02</v>
+      </c>
+      <c r="AD206">
+        <v>17</v>
+      </c>
+      <c r="AE206">
+        <v>1.2</v>
+      </c>
+      <c r="AF206">
+        <v>4.5</v>
+      </c>
+      <c r="AG206">
+        <v>1.62</v>
+      </c>
+      <c r="AH206">
+        <v>2.25</v>
+      </c>
+      <c r="AI206">
+        <v>1.57</v>
+      </c>
+      <c r="AJ206">
+        <v>2.25</v>
+      </c>
+      <c r="AK206">
+        <v>1.3</v>
+      </c>
+      <c r="AL206">
+        <v>1.2</v>
+      </c>
+      <c r="AM206">
+        <v>1.95</v>
+      </c>
+      <c r="AN206">
+        <v>1</v>
+      </c>
+      <c r="AO206">
+        <v>1.11</v>
+      </c>
+      <c r="AP206">
+        <v>0.91</v>
+      </c>
+      <c r="AQ206">
+        <v>1.3</v>
+      </c>
+      <c r="AR206">
+        <v>1.66</v>
+      </c>
+      <c r="AS206">
+        <v>1.3</v>
+      </c>
+      <c r="AT206">
+        <v>2.96</v>
+      </c>
+      <c r="AU206">
+        <v>9</v>
+      </c>
+      <c r="AV206">
+        <v>8</v>
+      </c>
+      <c r="AW206">
+        <v>14</v>
+      </c>
+      <c r="AX206">
+        <v>5</v>
+      </c>
+      <c r="AY206">
+        <v>23</v>
+      </c>
+      <c r="AZ206">
+        <v>13</v>
+      </c>
+      <c r="BA206">
+        <v>9</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>13</v>
+      </c>
+      <c r="BD206">
+        <v>1.68</v>
+      </c>
+      <c r="BE206">
+        <v>6.5</v>
+      </c>
+      <c r="BF206">
+        <v>2.43</v>
+      </c>
+      <c r="BG206">
+        <v>1.33</v>
+      </c>
+      <c r="BH206">
+        <v>2.95</v>
+      </c>
+      <c r="BI206">
+        <v>1.57</v>
+      </c>
+      <c r="BJ206">
+        <v>2.23</v>
+      </c>
+      <c r="BK206">
+        <v>1.93</v>
+      </c>
+      <c r="BL206">
+        <v>1.76</v>
+      </c>
+      <c r="BM206">
+        <v>2.43</v>
+      </c>
+      <c r="BN206">
+        <v>1.49</v>
+      </c>
+      <c r="BO206">
+        <v>3.15</v>
+      </c>
+      <c r="BP206">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -701,6 +701,9 @@
   </si>
   <si>
     <t>['9']</t>
+  </si>
+  <si>
+    <t>['58', '66']</t>
   </si>
   <si>
     <t>['5', '18']</t>
@@ -1392,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1854,7 +1857,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2060,7 +2063,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2266,7 +2269,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2472,7 +2475,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2678,7 +2681,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2884,7 +2887,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3090,7 +3093,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3374,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ10">
         <v>1.18</v>
@@ -3502,7 +3505,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3583,7 +3586,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ11">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3914,7 +3917,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4532,7 +4535,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5356,7 +5359,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6386,7 +6389,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6592,7 +6595,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6798,7 +6801,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -6879,7 +6882,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ27">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7210,7 +7213,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7494,7 +7497,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ30">
         <v>1.45</v>
@@ -7622,7 +7625,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8240,7 +8243,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8446,7 +8449,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9064,7 +9067,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9270,7 +9273,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9682,7 +9685,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10300,7 +10303,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10381,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10506,7 +10509,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10712,7 +10715,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10918,7 +10921,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -10996,7 +10999,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ47">
         <v>0.9</v>
@@ -11124,7 +11127,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11536,7 +11539,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11742,7 +11745,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11948,7 +11951,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12772,7 +12775,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13184,7 +13187,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13390,7 +13393,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13802,7 +13805,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14008,7 +14011,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14214,7 +14217,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14832,7 +14835,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15244,7 +15247,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15325,7 +15328,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ68">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15450,7 +15453,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15656,7 +15659,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15734,7 +15737,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15862,7 +15865,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16068,7 +16071,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16274,7 +16277,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16480,7 +16483,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16686,7 +16689,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17304,7 +17307,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17510,7 +17513,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17922,7 +17925,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18334,7 +18337,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18540,7 +18543,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19158,7 +19161,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19236,7 +19239,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ87">
         <v>1.55</v>
@@ -19364,7 +19367,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q88">
         <v>2.1</v>
@@ -19776,7 +19779,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20063,7 +20066,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20188,7 +20191,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20600,7 +20603,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20678,7 +20681,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ94">
         <v>1.6</v>
@@ -20806,7 +20809,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21012,7 +21015,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21218,7 +21221,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21630,7 +21633,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22042,7 +22045,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22248,7 +22251,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22660,7 +22663,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23072,7 +23075,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23896,7 +23899,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24102,7 +24105,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24308,7 +24311,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24720,7 +24723,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24926,7 +24929,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25007,7 +25010,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ115">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25132,7 +25135,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25338,7 +25341,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25544,7 +25547,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25750,7 +25753,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25956,7 +25959,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26162,7 +26165,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26368,7 +26371,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26446,7 +26449,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ122">
         <v>2.2</v>
@@ -26574,7 +26577,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26780,7 +26783,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -26986,7 +26989,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27398,7 +27401,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27604,7 +27607,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28016,7 +28019,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28222,7 +28225,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28634,7 +28637,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29252,7 +29255,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29333,7 +29336,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -30694,7 +30697,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30900,7 +30903,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31106,7 +31109,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31312,7 +31315,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31518,7 +31521,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31724,7 +31727,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32136,7 +32139,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32342,7 +32345,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32754,7 +32757,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32832,7 +32835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ153">
         <v>1.11</v>
@@ -32960,7 +32963,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33166,7 +33169,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33659,7 +33662,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ157">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34196,7 +34199,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34608,7 +34611,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34895,7 +34898,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ163">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35226,7 +35229,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35432,7 +35435,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35638,7 +35641,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35844,7 +35847,7 @@
         <v>92</v>
       </c>
       <c r="P168" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -36050,7 +36053,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36256,7 +36259,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36462,7 +36465,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36540,7 +36543,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ171">
         <v>0.64</v>
@@ -36874,7 +36877,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37080,7 +37083,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37698,7 +37701,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37904,7 +37907,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38316,7 +38319,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38522,7 +38525,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39140,7 +39143,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39218,7 +39221,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ184">
         <v>2.11</v>
@@ -39346,7 +39349,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39552,7 +39555,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40170,7 +40173,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40251,7 +40254,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ189">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40582,7 +40585,7 @@
         <v>220</v>
       </c>
       <c r="P191" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40788,7 +40791,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -40994,7 +40997,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41200,7 +41203,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41406,7 +41409,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41612,7 +41615,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42024,7 +42027,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42230,7 +42233,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42642,7 +42645,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42848,7 +42851,7 @@
         <v>140</v>
       </c>
       <c r="P202" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43672,7 +43675,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43829,6 +43832,212 @@
       </c>
       <c r="BP206">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7465622</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45670.66666666666</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>78</v>
+      </c>
+      <c r="H207" t="s">
+        <v>89</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>3</v>
+      </c>
+      <c r="O207" t="s">
+        <v>229</v>
+      </c>
+      <c r="P207" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q207">
+        <v>2.75</v>
+      </c>
+      <c r="R207">
+        <v>2.5</v>
+      </c>
+      <c r="S207">
+        <v>3.1</v>
+      </c>
+      <c r="T207">
+        <v>1.22</v>
+      </c>
+      <c r="U207">
+        <v>4</v>
+      </c>
+      <c r="V207">
+        <v>2.1</v>
+      </c>
+      <c r="W207">
+        <v>1.67</v>
+      </c>
+      <c r="X207">
+        <v>4.5</v>
+      </c>
+      <c r="Y207">
+        <v>1.18</v>
+      </c>
+      <c r="Z207">
+        <v>2.25</v>
+      </c>
+      <c r="AA207">
+        <v>3.8</v>
+      </c>
+      <c r="AB207">
+        <v>2.75</v>
+      </c>
+      <c r="AC207">
+        <v>1.01</v>
+      </c>
+      <c r="AD207">
+        <v>17</v>
+      </c>
+      <c r="AE207">
+        <v>1.12</v>
+      </c>
+      <c r="AF207">
+        <v>6.5</v>
+      </c>
+      <c r="AG207">
+        <v>1.4</v>
+      </c>
+      <c r="AH207">
+        <v>2.88</v>
+      </c>
+      <c r="AI207">
+        <v>1.4</v>
+      </c>
+      <c r="AJ207">
+        <v>2.75</v>
+      </c>
+      <c r="AK207">
+        <v>1.39</v>
+      </c>
+      <c r="AL207">
+        <v>1.23</v>
+      </c>
+      <c r="AM207">
+        <v>1.7</v>
+      </c>
+      <c r="AN207">
+        <v>0.9</v>
+      </c>
+      <c r="AO207">
+        <v>0.9</v>
+      </c>
+      <c r="AP207">
+        <v>1.09</v>
+      </c>
+      <c r="AQ207">
+        <v>0.82</v>
+      </c>
+      <c r="AR207">
+        <v>1.77</v>
+      </c>
+      <c r="AS207">
+        <v>1.5</v>
+      </c>
+      <c r="AT207">
+        <v>3.27</v>
+      </c>
+      <c r="AU207">
+        <v>7</v>
+      </c>
+      <c r="AV207">
+        <v>5</v>
+      </c>
+      <c r="AW207">
+        <v>6</v>
+      </c>
+      <c r="AX207">
+        <v>15</v>
+      </c>
+      <c r="AY207">
+        <v>13</v>
+      </c>
+      <c r="AZ207">
+        <v>20</v>
+      </c>
+      <c r="BA207">
+        <v>2</v>
+      </c>
+      <c r="BB207">
+        <v>3</v>
+      </c>
+      <c r="BC207">
+        <v>5</v>
+      </c>
+      <c r="BD207">
+        <v>1.84</v>
+      </c>
+      <c r="BE207">
+        <v>6.75</v>
+      </c>
+      <c r="BF207">
+        <v>2.15</v>
+      </c>
+      <c r="BG207">
+        <v>1.27</v>
+      </c>
+      <c r="BH207">
+        <v>3.4</v>
+      </c>
+      <c r="BI207">
+        <v>1.47</v>
+      </c>
+      <c r="BJ207">
+        <v>2.48</v>
+      </c>
+      <c r="BK207">
+        <v>1.76</v>
+      </c>
+      <c r="BL207">
+        <v>1.94</v>
+      </c>
+      <c r="BM207">
+        <v>2.18</v>
+      </c>
+      <c r="BN207">
+        <v>1.58</v>
+      </c>
+      <c r="BO207">
+        <v>2.8</v>
+      </c>
+      <c r="BP207">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="346">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,21 @@
     <t>['58', '66']</t>
   </si>
   <si>
+    <t>['17', '56', '67']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['5', '43', '45', '58']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['3', '19', '31', '40', '56']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -854,9 +869,6 @@
   </si>
   <si>
     <t>['19', '57', '64']</t>
-  </si>
-  <si>
-    <t>['78']</t>
   </si>
   <si>
     <t>['35', '90+5']</t>
@@ -1034,6 +1046,12 @@
   </si>
   <si>
     <t>['10', '13', '57', '75']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['30', '77']</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1750,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ2">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1857,7 +1875,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2063,7 +2081,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2269,7 +2287,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2347,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ5">
         <v>2.2</v>
@@ -2475,7 +2493,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2553,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2681,7 +2699,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2762,7 +2780,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ7">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2887,7 +2905,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2965,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1.3</v>
@@ -3093,7 +3111,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3380,7 +3398,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3505,7 +3523,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3789,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ12">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3917,7 +3935,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4535,7 +4553,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4822,7 +4840,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5025,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ18">
         <v>1.11</v>
@@ -5231,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5359,7 +5377,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5437,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ20">
         <v>2.11</v>
@@ -5849,7 +5867,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
         <v>2.2</v>
@@ -6058,7 +6076,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ23">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6389,7 +6407,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6595,7 +6613,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6673,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.73</v>
@@ -6801,7 +6819,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7088,7 +7106,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ28">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7213,7 +7231,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7291,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ29">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7625,7 +7643,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7706,7 +7724,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ31">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -8118,7 +8136,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ33">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8243,7 +8261,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8321,7 +8339,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
         <v>1.18</v>
@@ -8449,7 +8467,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8939,7 +8957,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ37">
         <v>2.2</v>
@@ -9067,7 +9085,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9145,10 +9163,10 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9273,7 +9291,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9354,7 +9372,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9557,7 +9575,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ40">
         <v>0.5</v>
@@ -9685,7 +9703,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10303,7 +10321,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10381,7 +10399,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ44">
         <v>0.82</v>
@@ -10509,7 +10527,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10587,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ45">
         <v>0.5600000000000001</v>
@@ -10715,7 +10733,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10793,7 +10811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46">
         <v>1.18</v>
@@ -10921,7 +10939,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11002,7 +11020,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ47">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11127,7 +11145,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11205,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48">
         <v>1.73</v>
@@ -11539,7 +11557,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11620,7 +11638,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ50">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -11745,7 +11763,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11826,7 +11844,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ51">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11951,7 +11969,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12032,7 +12050,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ52">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12441,10 +12459,10 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -12775,7 +12793,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -12856,7 +12874,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ56">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13187,7 +13205,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13268,7 +13286,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ58">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13393,7 +13411,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13677,7 +13695,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ60">
         <v>1.45</v>
@@ -13805,7 +13823,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -13886,7 +13904,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14011,7 +14029,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14089,7 +14107,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ62">
         <v>1.18</v>
@@ -14217,7 +14235,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14707,10 +14725,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14835,7 +14853,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14913,10 +14931,10 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15247,7 +15265,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15453,7 +15471,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15531,7 +15549,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
         <v>1.55</v>
@@ -15659,7 +15677,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15865,7 +15883,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16071,7 +16089,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16149,7 +16167,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ72">
         <v>1.3</v>
@@ -16277,7 +16295,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16355,7 +16373,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73">
         <v>0.5</v>
@@ -16483,7 +16501,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16564,7 +16582,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ74">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -16689,7 +16707,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16767,7 +16785,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0.5600000000000001</v>
@@ -16976,7 +16994,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ76">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17182,7 +17200,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ77">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17307,7 +17325,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17388,7 +17406,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ78">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17513,7 +17531,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17591,7 +17609,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ79">
         <v>2.11</v>
@@ -17925,7 +17943,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18006,7 +18024,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ81">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18209,7 +18227,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ82">
         <v>2.2</v>
@@ -18337,7 +18355,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18543,7 +18561,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18621,7 +18639,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>1.11</v>
@@ -18830,7 +18848,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ85">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19036,7 +19054,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ86">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19161,7 +19179,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19367,7 +19385,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="Q88">
         <v>2.1</v>
@@ -19651,7 +19669,7 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ89">
         <v>1.18</v>
@@ -19779,7 +19797,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20191,7 +20209,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20475,7 +20493,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ93">
         <v>1.3</v>
@@ -20603,7 +20621,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20684,7 +20702,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -20809,7 +20827,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20887,7 +20905,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ95">
         <v>1.45</v>
@@ -21015,7 +21033,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21093,10 +21111,10 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21221,7 +21239,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21299,7 +21317,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ97">
         <v>1.73</v>
@@ -21633,7 +21651,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21920,7 +21938,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ100">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22045,7 +22063,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22251,7 +22269,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22535,10 +22553,10 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22663,7 +22681,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22744,7 +22762,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ104">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23075,7 +23093,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23156,7 +23174,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23359,7 +23377,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
         <v>1.55</v>
@@ -23774,7 +23792,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ109">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -23899,7 +23917,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23977,10 +23995,10 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ110">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24105,7 +24123,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24183,10 +24201,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ111">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24311,7 +24329,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24389,7 +24407,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24595,7 +24613,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ113">
         <v>0.5600000000000001</v>
@@ -24723,7 +24741,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24801,7 +24819,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ114">
         <v>1.55</v>
@@ -24929,7 +24947,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25135,7 +25153,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25213,10 +25231,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25341,7 +25359,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25547,7 +25565,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25625,10 +25643,10 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ118">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25753,7 +25771,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25959,7 +25977,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26040,7 +26058,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ120">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26165,7 +26183,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26243,10 +26261,10 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ121">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26371,7 +26389,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26577,7 +26595,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26783,7 +26801,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -26989,7 +27007,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27401,7 +27419,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27482,7 +27500,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ127">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27607,7 +27625,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27894,7 +27912,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28019,7 +28037,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28225,7 +28243,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28509,7 +28527,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28637,7 +28655,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28715,10 +28733,10 @@
         <v>1.17</v>
       </c>
       <c r="AP133">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ133">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -28921,10 +28939,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ134">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29127,7 +29145,7 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ135">
         <v>1.18</v>
@@ -29255,7 +29273,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29745,10 +29763,10 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -29951,7 +29969,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ139">
         <v>0.5600000000000001</v>
@@ -30160,7 +30178,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -30363,10 +30381,10 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ141">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -30697,7 +30715,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30903,7 +30921,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30981,7 +30999,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ144">
         <v>1.45</v>
@@ -31109,7 +31127,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31315,7 +31333,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31393,7 +31411,7 @@
         <v>2.5</v>
       </c>
       <c r="AP146">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ146">
         <v>2.11</v>
@@ -31521,7 +31539,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31727,7 +31745,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31808,7 +31826,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ148">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32014,7 +32032,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ149">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32139,7 +32157,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32345,7 +32363,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32426,7 +32444,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ151">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -32757,7 +32775,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32963,7 +32981,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33044,7 +33062,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ154">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33169,7 +33187,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33247,7 +33265,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ155">
         <v>0.5</v>
@@ -33659,7 +33677,7 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ157">
         <v>0.82</v>
@@ -34074,7 +34092,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ159">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34199,7 +34217,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34277,10 +34295,10 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ160">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34486,7 +34504,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ161">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34611,7 +34629,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34689,7 +34707,7 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ162">
         <v>2.11</v>
@@ -35229,7 +35247,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35435,7 +35453,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35641,7 +35659,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35722,7 +35740,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ167">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -35847,7 +35865,7 @@
         <v>92</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35925,7 +35943,7 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168">
         <v>0.5600000000000001</v>
@@ -36053,7 +36071,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36259,7 +36277,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36465,7 +36483,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36749,7 +36767,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ172">
         <v>0.5</v>
@@ -36877,7 +36895,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -36955,10 +36973,10 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ173">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37083,7 +37101,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37161,10 +37179,10 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ174">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -37367,10 +37385,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ175">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -37576,7 +37594,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -37701,7 +37719,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37779,7 +37797,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ177">
         <v>1.11</v>
@@ -37907,7 +37925,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37988,7 +38006,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ178">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38319,7 +38337,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38525,7 +38543,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38606,7 +38624,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ181">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -38812,7 +38830,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ182">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39143,7 +39161,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39349,7 +39367,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39555,7 +39573,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40045,7 +40063,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ188">
         <v>0.64</v>
@@ -40173,7 +40191,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40251,7 +40269,7 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ189">
         <v>0.82</v>
@@ -40585,7 +40603,7 @@
         <v>220</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40791,7 +40809,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -40872,7 +40890,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ192">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -40997,7 +41015,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41078,7 +41096,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ193">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41203,7 +41221,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41281,10 +41299,10 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ194">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41409,7 +41427,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41487,7 +41505,7 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ195">
         <v>1.55</v>
@@ -41615,7 +41633,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41696,7 +41714,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ196">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -41899,10 +41917,10 @@
         <v>1.6</v>
       </c>
       <c r="AP197">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ197">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42027,7 +42045,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42105,7 +42123,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42233,7 +42251,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42311,10 +42329,10 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ199">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42517,7 +42535,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>0.5</v>
@@ -42645,7 +42663,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42726,7 +42744,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ201">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -42851,7 +42869,7 @@
         <v>140</v>
       </c>
       <c r="P202" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43135,7 +43153,7 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ203">
         <v>0.64</v>
@@ -43675,7 +43693,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43881,7 +43899,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44038,6 +44056,1448 @@
       </c>
       <c r="BP207">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7465623</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F208">
+        <v>22</v>
+      </c>
+      <c r="G208" t="s">
+        <v>76</v>
+      </c>
+      <c r="H208" t="s">
+        <v>72</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>4</v>
+      </c>
+      <c r="O208" t="s">
+        <v>230</v>
+      </c>
+      <c r="P208" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q208">
+        <v>1.93</v>
+      </c>
+      <c r="R208">
+        <v>2.45</v>
+      </c>
+      <c r="S208">
+        <v>5.25</v>
+      </c>
+      <c r="T208">
+        <v>1.25</v>
+      </c>
+      <c r="U208">
+        <v>3.45</v>
+      </c>
+      <c r="V208">
+        <v>2.2</v>
+      </c>
+      <c r="W208">
+        <v>1.6</v>
+      </c>
+      <c r="X208">
+        <v>4.75</v>
+      </c>
+      <c r="Y208">
+        <v>1.16</v>
+      </c>
+      <c r="Z208">
+        <v>1.45</v>
+      </c>
+      <c r="AA208">
+        <v>4.5</v>
+      </c>
+      <c r="AB208">
+        <v>6.25</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>13</v>
+      </c>
+      <c r="AE208">
+        <v>1.17</v>
+      </c>
+      <c r="AF208">
+        <v>5</v>
+      </c>
+      <c r="AG208">
+        <v>1.5</v>
+      </c>
+      <c r="AH208">
+        <v>2.5</v>
+      </c>
+      <c r="AI208">
+        <v>1.6</v>
+      </c>
+      <c r="AJ208">
+        <v>2.15</v>
+      </c>
+      <c r="AK208">
+        <v>1.11</v>
+      </c>
+      <c r="AL208">
+        <v>1.15</v>
+      </c>
+      <c r="AM208">
+        <v>2.6</v>
+      </c>
+      <c r="AN208">
+        <v>1.91</v>
+      </c>
+      <c r="AO208">
+        <v>1.6</v>
+      </c>
+      <c r="AP208">
+        <v>2</v>
+      </c>
+      <c r="AQ208">
+        <v>1.45</v>
+      </c>
+      <c r="AR208">
+        <v>1.86</v>
+      </c>
+      <c r="AS208">
+        <v>1.29</v>
+      </c>
+      <c r="AT208">
+        <v>3.15</v>
+      </c>
+      <c r="AU208">
+        <v>7</v>
+      </c>
+      <c r="AV208">
+        <v>7</v>
+      </c>
+      <c r="AW208">
+        <v>4</v>
+      </c>
+      <c r="AX208">
+        <v>8</v>
+      </c>
+      <c r="AY208">
+        <v>12</v>
+      </c>
+      <c r="AZ208">
+        <v>18</v>
+      </c>
+      <c r="BA208">
+        <v>2</v>
+      </c>
+      <c r="BB208">
+        <v>4</v>
+      </c>
+      <c r="BC208">
+        <v>6</v>
+      </c>
+      <c r="BD208">
+        <v>1.43</v>
+      </c>
+      <c r="BE208">
+        <v>7</v>
+      </c>
+      <c r="BF208">
+        <v>3.15</v>
+      </c>
+      <c r="BG208">
+        <v>1.32</v>
+      </c>
+      <c r="BH208">
+        <v>3.05</v>
+      </c>
+      <c r="BI208">
+        <v>1.55</v>
+      </c>
+      <c r="BJ208">
+        <v>2.28</v>
+      </c>
+      <c r="BK208">
+        <v>1.9</v>
+      </c>
+      <c r="BL208">
+        <v>1.79</v>
+      </c>
+      <c r="BM208">
+        <v>2.38</v>
+      </c>
+      <c r="BN208">
+        <v>1.5</v>
+      </c>
+      <c r="BO208">
+        <v>3.05</v>
+      </c>
+      <c r="BP208">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7465625</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F209">
+        <v>22</v>
+      </c>
+      <c r="G209" t="s">
+        <v>86</v>
+      </c>
+      <c r="H209" t="s">
+        <v>78</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>231</v>
+      </c>
+      <c r="P209" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q209">
+        <v>2.2</v>
+      </c>
+      <c r="R209">
+        <v>2.6</v>
+      </c>
+      <c r="S209">
+        <v>4.33</v>
+      </c>
+      <c r="T209">
+        <v>1.22</v>
+      </c>
+      <c r="U209">
+        <v>4</v>
+      </c>
+      <c r="V209">
+        <v>2.1</v>
+      </c>
+      <c r="W209">
+        <v>1.67</v>
+      </c>
+      <c r="X209">
+        <v>4.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.18</v>
+      </c>
+      <c r="Z209">
+        <v>1.65</v>
+      </c>
+      <c r="AA209">
+        <v>4.29</v>
+      </c>
+      <c r="AB209">
+        <v>4.32</v>
+      </c>
+      <c r="AC209">
+        <v>1.01</v>
+      </c>
+      <c r="AD209">
+        <v>17</v>
+      </c>
+      <c r="AE209">
+        <v>1.11</v>
+      </c>
+      <c r="AF209">
+        <v>6.5</v>
+      </c>
+      <c r="AG209">
+        <v>1.4</v>
+      </c>
+      <c r="AH209">
+        <v>2.88</v>
+      </c>
+      <c r="AI209">
+        <v>1.44</v>
+      </c>
+      <c r="AJ209">
+        <v>2.63</v>
+      </c>
+      <c r="AK209">
+        <v>1.22</v>
+      </c>
+      <c r="AL209">
+        <v>1.2</v>
+      </c>
+      <c r="AM209">
+        <v>2.1</v>
+      </c>
+      <c r="AN209">
+        <v>2</v>
+      </c>
+      <c r="AO209">
+        <v>1.3</v>
+      </c>
+      <c r="AP209">
+        <v>1.91</v>
+      </c>
+      <c r="AQ209">
+        <v>1.27</v>
+      </c>
+      <c r="AR209">
+        <v>1.87</v>
+      </c>
+      <c r="AS209">
+        <v>1.31</v>
+      </c>
+      <c r="AT209">
+        <v>3.18</v>
+      </c>
+      <c r="AU209">
+        <v>5</v>
+      </c>
+      <c r="AV209">
+        <v>7</v>
+      </c>
+      <c r="AW209">
+        <v>2</v>
+      </c>
+      <c r="AX209">
+        <v>1</v>
+      </c>
+      <c r="AY209">
+        <v>10</v>
+      </c>
+      <c r="AZ209">
+        <v>14</v>
+      </c>
+      <c r="BA209">
+        <v>5</v>
+      </c>
+      <c r="BB209">
+        <v>7</v>
+      </c>
+      <c r="BC209">
+        <v>12</v>
+      </c>
+      <c r="BD209">
+        <v>1.55</v>
+      </c>
+      <c r="BE209">
+        <v>6.5</v>
+      </c>
+      <c r="BF209">
+        <v>2.7</v>
+      </c>
+      <c r="BG209">
+        <v>1.25</v>
+      </c>
+      <c r="BH209">
+        <v>3.4</v>
+      </c>
+      <c r="BI209">
+        <v>1.45</v>
+      </c>
+      <c r="BJ209">
+        <v>2.55</v>
+      </c>
+      <c r="BK209">
+        <v>1.72</v>
+      </c>
+      <c r="BL209">
+        <v>1.98</v>
+      </c>
+      <c r="BM209">
+        <v>2.1</v>
+      </c>
+      <c r="BN209">
+        <v>1.64</v>
+      </c>
+      <c r="BO209">
+        <v>2.65</v>
+      </c>
+      <c r="BP209">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7465626</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F210">
+        <v>22</v>
+      </c>
+      <c r="G210" t="s">
+        <v>88</v>
+      </c>
+      <c r="H210" t="s">
+        <v>75</v>
+      </c>
+      <c r="I210">
+        <v>3</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>3</v>
+      </c>
+      <c r="L210">
+        <v>4</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>4</v>
+      </c>
+      <c r="O210" t="s">
+        <v>232</v>
+      </c>
+      <c r="P210" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q210">
+        <v>1.83</v>
+      </c>
+      <c r="R210">
+        <v>2.65</v>
+      </c>
+      <c r="S210">
+        <v>5</v>
+      </c>
+      <c r="T210">
+        <v>1.2</v>
+      </c>
+      <c r="U210">
+        <v>4</v>
+      </c>
+      <c r="V210">
+        <v>1.95</v>
+      </c>
+      <c r="W210">
+        <v>1.75</v>
+      </c>
+      <c r="X210">
+        <v>4.25</v>
+      </c>
+      <c r="Y210">
+        <v>1.2</v>
+      </c>
+      <c r="Z210">
+        <v>1.4</v>
+      </c>
+      <c r="AA210">
+        <v>5</v>
+      </c>
+      <c r="AB210">
+        <v>6.5</v>
+      </c>
+      <c r="AC210">
+        <v>1.01</v>
+      </c>
+      <c r="AD210">
+        <v>23</v>
+      </c>
+      <c r="AE210">
+        <v>1.1</v>
+      </c>
+      <c r="AF210">
+        <v>6.5</v>
+      </c>
+      <c r="AG210">
+        <v>1.38</v>
+      </c>
+      <c r="AH210">
+        <v>3</v>
+      </c>
+      <c r="AI210">
+        <v>1.48</v>
+      </c>
+      <c r="AJ210">
+        <v>2.4</v>
+      </c>
+      <c r="AK210">
+        <v>1.11</v>
+      </c>
+      <c r="AL210">
+        <v>1.12</v>
+      </c>
+      <c r="AM210">
+        <v>2.8</v>
+      </c>
+      <c r="AN210">
+        <v>2.4</v>
+      </c>
+      <c r="AO210">
+        <v>0.9</v>
+      </c>
+      <c r="AP210">
+        <v>2.45</v>
+      </c>
+      <c r="AQ210">
+        <v>0.82</v>
+      </c>
+      <c r="AR210">
+        <v>1.95</v>
+      </c>
+      <c r="AS210">
+        <v>1.4</v>
+      </c>
+      <c r="AT210">
+        <v>3.35</v>
+      </c>
+      <c r="AU210">
+        <v>6</v>
+      </c>
+      <c r="AV210">
+        <v>7</v>
+      </c>
+      <c r="AW210">
+        <v>6</v>
+      </c>
+      <c r="AX210">
+        <v>5</v>
+      </c>
+      <c r="AY210">
+        <v>15</v>
+      </c>
+      <c r="AZ210">
+        <v>17</v>
+      </c>
+      <c r="BA210">
+        <v>2</v>
+      </c>
+      <c r="BB210">
+        <v>13</v>
+      </c>
+      <c r="BC210">
+        <v>15</v>
+      </c>
+      <c r="BD210">
+        <v>1.38</v>
+      </c>
+      <c r="BE210">
+        <v>7.5</v>
+      </c>
+      <c r="BF210">
+        <v>3.4</v>
+      </c>
+      <c r="BG210">
+        <v>1.23</v>
+      </c>
+      <c r="BH210">
+        <v>3.65</v>
+      </c>
+      <c r="BI210">
+        <v>1.42</v>
+      </c>
+      <c r="BJ210">
+        <v>2.65</v>
+      </c>
+      <c r="BK210">
+        <v>1.67</v>
+      </c>
+      <c r="BL210">
+        <v>2.07</v>
+      </c>
+      <c r="BM210">
+        <v>2.02</v>
+      </c>
+      <c r="BN210">
+        <v>1.7</v>
+      </c>
+      <c r="BO210">
+        <v>2.55</v>
+      </c>
+      <c r="BP210">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7465627</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F211">
+        <v>22</v>
+      </c>
+      <c r="G211" t="s">
+        <v>87</v>
+      </c>
+      <c r="H211" t="s">
+        <v>83</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
+        <v>130</v>
+      </c>
+      <c r="P211" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q211">
+        <v>3</v>
+      </c>
+      <c r="R211">
+        <v>2.15</v>
+      </c>
+      <c r="S211">
+        <v>3.1</v>
+      </c>
+      <c r="T211">
+        <v>1.33</v>
+      </c>
+      <c r="U211">
+        <v>3</v>
+      </c>
+      <c r="V211">
+        <v>2.4</v>
+      </c>
+      <c r="W211">
+        <v>1.5</v>
+      </c>
+      <c r="X211">
+        <v>5.75</v>
+      </c>
+      <c r="Y211">
+        <v>1.12</v>
+      </c>
+      <c r="Z211">
+        <v>2.5</v>
+      </c>
+      <c r="AA211">
+        <v>3.5</v>
+      </c>
+      <c r="AB211">
+        <v>2.6</v>
+      </c>
+      <c r="AC211">
+        <v>1.04</v>
+      </c>
+      <c r="AD211">
+        <v>10</v>
+      </c>
+      <c r="AE211">
+        <v>1.22</v>
+      </c>
+      <c r="AF211">
+        <v>4.2</v>
+      </c>
+      <c r="AG211">
+        <v>1.67</v>
+      </c>
+      <c r="AH211">
+        <v>2.15</v>
+      </c>
+      <c r="AI211">
+        <v>1.5</v>
+      </c>
+      <c r="AJ211">
+        <v>2.35</v>
+      </c>
+      <c r="AK211">
+        <v>1.48</v>
+      </c>
+      <c r="AL211">
+        <v>1.25</v>
+      </c>
+      <c r="AM211">
+        <v>1.5</v>
+      </c>
+      <c r="AN211">
+        <v>1</v>
+      </c>
+      <c r="AO211">
+        <v>1.55</v>
+      </c>
+      <c r="AP211">
+        <v>1.18</v>
+      </c>
+      <c r="AQ211">
+        <v>1.42</v>
+      </c>
+      <c r="AR211">
+        <v>1.76</v>
+      </c>
+      <c r="AS211">
+        <v>1.77</v>
+      </c>
+      <c r="AT211">
+        <v>3.53</v>
+      </c>
+      <c r="AU211">
+        <v>8</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>7</v>
+      </c>
+      <c r="AX211">
+        <v>6</v>
+      </c>
+      <c r="AY211">
+        <v>18</v>
+      </c>
+      <c r="AZ211">
+        <v>15</v>
+      </c>
+      <c r="BA211">
+        <v>2</v>
+      </c>
+      <c r="BB211">
+        <v>6</v>
+      </c>
+      <c r="BC211">
+        <v>8</v>
+      </c>
+      <c r="BD211">
+        <v>1.91</v>
+      </c>
+      <c r="BE211">
+        <v>6.4</v>
+      </c>
+      <c r="BF211">
+        <v>2.08</v>
+      </c>
+      <c r="BG211">
+        <v>1.34</v>
+      </c>
+      <c r="BH211">
+        <v>2.9</v>
+      </c>
+      <c r="BI211">
+        <v>1.58</v>
+      </c>
+      <c r="BJ211">
+        <v>2.18</v>
+      </c>
+      <c r="BK211">
+        <v>1.95</v>
+      </c>
+      <c r="BL211">
+        <v>1.75</v>
+      </c>
+      <c r="BM211">
+        <v>2.45</v>
+      </c>
+      <c r="BN211">
+        <v>1.48</v>
+      </c>
+      <c r="BO211">
+        <v>3.15</v>
+      </c>
+      <c r="BP211">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7465628</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>74</v>
+      </c>
+      <c r="H212" t="s">
+        <v>82</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>2</v>
+      </c>
+      <c r="N212">
+        <v>2</v>
+      </c>
+      <c r="O212" t="s">
+        <v>93</v>
+      </c>
+      <c r="P212" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q212">
+        <v>4.2</v>
+      </c>
+      <c r="R212">
+        <v>2.25</v>
+      </c>
+      <c r="S212">
+        <v>2.3</v>
+      </c>
+      <c r="T212">
+        <v>1.33</v>
+      </c>
+      <c r="U212">
+        <v>3.1</v>
+      </c>
+      <c r="V212">
+        <v>2.45</v>
+      </c>
+      <c r="W212">
+        <v>1.48</v>
+      </c>
+      <c r="X212">
+        <v>5.45</v>
+      </c>
+      <c r="Y212">
+        <v>1.13</v>
+      </c>
+      <c r="Z212">
+        <v>4</v>
+      </c>
+      <c r="AA212">
+        <v>3.75</v>
+      </c>
+      <c r="AB212">
+        <v>1.8</v>
+      </c>
+      <c r="AC212">
+        <v>1.04</v>
+      </c>
+      <c r="AD212">
+        <v>10</v>
+      </c>
+      <c r="AE212">
+        <v>1.22</v>
+      </c>
+      <c r="AF212">
+        <v>4.2</v>
+      </c>
+      <c r="AG212">
+        <v>1.67</v>
+      </c>
+      <c r="AH212">
+        <v>2.15</v>
+      </c>
+      <c r="AI212">
+        <v>1.57</v>
+      </c>
+      <c r="AJ212">
+        <v>2.2</v>
+      </c>
+      <c r="AK212">
+        <v>1.95</v>
+      </c>
+      <c r="AL212">
+        <v>1.2</v>
+      </c>
+      <c r="AM212">
+        <v>1.22</v>
+      </c>
+      <c r="AN212">
+        <v>1.82</v>
+      </c>
+      <c r="AO212">
+        <v>1.18</v>
+      </c>
+      <c r="AP212">
+        <v>1.67</v>
+      </c>
+      <c r="AQ212">
+        <v>1.33</v>
+      </c>
+      <c r="AR212">
+        <v>1.37</v>
+      </c>
+      <c r="AS212">
+        <v>1.68</v>
+      </c>
+      <c r="AT212">
+        <v>3.05</v>
+      </c>
+      <c r="AU212">
+        <v>8</v>
+      </c>
+      <c r="AV212">
+        <v>8</v>
+      </c>
+      <c r="AW212">
+        <v>7</v>
+      </c>
+      <c r="AX212">
+        <v>6</v>
+      </c>
+      <c r="AY212">
+        <v>23</v>
+      </c>
+      <c r="AZ212">
+        <v>21</v>
+      </c>
+      <c r="BA212">
+        <v>9</v>
+      </c>
+      <c r="BB212">
+        <v>7</v>
+      </c>
+      <c r="BC212">
+        <v>16</v>
+      </c>
+      <c r="BD212">
+        <v>2.8</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>1.53</v>
+      </c>
+      <c r="BG212">
+        <v>1.24</v>
+      </c>
+      <c r="BH212">
+        <v>3.55</v>
+      </c>
+      <c r="BI212">
+        <v>1.44</v>
+      </c>
+      <c r="BJ212">
+        <v>2.55</v>
+      </c>
+      <c r="BK212">
+        <v>1.72</v>
+      </c>
+      <c r="BL212">
+        <v>1.98</v>
+      </c>
+      <c r="BM212">
+        <v>2.12</v>
+      </c>
+      <c r="BN212">
+        <v>1.64</v>
+      </c>
+      <c r="BO212">
+        <v>2.65</v>
+      </c>
+      <c r="BP212">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7465629</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>80</v>
+      </c>
+      <c r="H213" t="s">
+        <v>81</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>1</v>
+      </c>
+      <c r="O213" t="s">
+        <v>233</v>
+      </c>
+      <c r="P213" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q213">
+        <v>3.4</v>
+      </c>
+      <c r="R213">
+        <v>2.15</v>
+      </c>
+      <c r="S213">
+        <v>2.75</v>
+      </c>
+      <c r="T213">
+        <v>1.33</v>
+      </c>
+      <c r="U213">
+        <v>3.1</v>
+      </c>
+      <c r="V213">
+        <v>2.4</v>
+      </c>
+      <c r="W213">
+        <v>1.5</v>
+      </c>
+      <c r="X213">
+        <v>5.8</v>
+      </c>
+      <c r="Y213">
+        <v>1.12</v>
+      </c>
+      <c r="Z213">
+        <v>3</v>
+      </c>
+      <c r="AA213">
+        <v>3.55</v>
+      </c>
+      <c r="AB213">
+        <v>2.2</v>
+      </c>
+      <c r="AC213">
+        <v>1.04</v>
+      </c>
+      <c r="AD213">
+        <v>10</v>
+      </c>
+      <c r="AE213">
+        <v>1.22</v>
+      </c>
+      <c r="AF213">
+        <v>4.2</v>
+      </c>
+      <c r="AG213">
+        <v>1.67</v>
+      </c>
+      <c r="AH213">
+        <v>2.15</v>
+      </c>
+      <c r="AI213">
+        <v>1.53</v>
+      </c>
+      <c r="AJ213">
+        <v>2.3</v>
+      </c>
+      <c r="AK213">
+        <v>1.62</v>
+      </c>
+      <c r="AL213">
+        <v>1.22</v>
+      </c>
+      <c r="AM213">
+        <v>1.38</v>
+      </c>
+      <c r="AN213">
+        <v>0.55</v>
+      </c>
+      <c r="AO213">
+        <v>1.09</v>
+      </c>
+      <c r="AP213">
+        <v>0.75</v>
+      </c>
+      <c r="AQ213">
+        <v>1</v>
+      </c>
+      <c r="AR213">
+        <v>1.58</v>
+      </c>
+      <c r="AS213">
+        <v>1.59</v>
+      </c>
+      <c r="AT213">
+        <v>3.17</v>
+      </c>
+      <c r="AU213">
+        <v>4</v>
+      </c>
+      <c r="AV213">
+        <v>4</v>
+      </c>
+      <c r="AW213">
+        <v>6</v>
+      </c>
+      <c r="AX213">
+        <v>4</v>
+      </c>
+      <c r="AY213">
+        <v>12</v>
+      </c>
+      <c r="AZ213">
+        <v>12</v>
+      </c>
+      <c r="BA213">
+        <v>4</v>
+      </c>
+      <c r="BB213">
+        <v>7</v>
+      </c>
+      <c r="BC213">
+        <v>11</v>
+      </c>
+      <c r="BD213">
+        <v>2.2</v>
+      </c>
+      <c r="BE213">
+        <v>6.4</v>
+      </c>
+      <c r="BF213">
+        <v>1.82</v>
+      </c>
+      <c r="BG213">
+        <v>1.34</v>
+      </c>
+      <c r="BH213">
+        <v>2.9</v>
+      </c>
+      <c r="BI213">
+        <v>1.57</v>
+      </c>
+      <c r="BJ213">
+        <v>2.23</v>
+      </c>
+      <c r="BK213">
+        <v>1.93</v>
+      </c>
+      <c r="BL213">
+        <v>1.76</v>
+      </c>
+      <c r="BM213">
+        <v>2.45</v>
+      </c>
+      <c r="BN213">
+        <v>1.48</v>
+      </c>
+      <c r="BO213">
+        <v>3.2</v>
+      </c>
+      <c r="BP213">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7465630</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45675.52083333334</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>73</v>
+      </c>
+      <c r="H214" t="s">
+        <v>85</v>
+      </c>
+      <c r="I214">
+        <v>4</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>4</v>
+      </c>
+      <c r="L214">
+        <v>5</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>5</v>
+      </c>
+      <c r="O214" t="s">
+        <v>234</v>
+      </c>
+      <c r="P214" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q214">
+        <v>2.7</v>
+      </c>
+      <c r="R214">
+        <v>2.2</v>
+      </c>
+      <c r="S214">
+        <v>3.35</v>
+      </c>
+      <c r="T214">
+        <v>1.3</v>
+      </c>
+      <c r="U214">
+        <v>3.25</v>
+      </c>
+      <c r="V214">
+        <v>2.3</v>
+      </c>
+      <c r="W214">
+        <v>1.55</v>
+      </c>
+      <c r="X214">
+        <v>5</v>
+      </c>
+      <c r="Y214">
+        <v>1.15</v>
+      </c>
+      <c r="Z214">
+        <v>2.2</v>
+      </c>
+      <c r="AA214">
+        <v>3.6</v>
+      </c>
+      <c r="AB214">
+        <v>2.95</v>
+      </c>
+      <c r="AC214">
+        <v>1.04</v>
+      </c>
+      <c r="AD214">
+        <v>10</v>
+      </c>
+      <c r="AE214">
+        <v>1.2</v>
+      </c>
+      <c r="AF214">
+        <v>4.5</v>
+      </c>
+      <c r="AG214">
+        <v>1.57</v>
+      </c>
+      <c r="AH214">
+        <v>2.35</v>
+      </c>
+      <c r="AI214">
+        <v>1.45</v>
+      </c>
+      <c r="AJ214">
+        <v>2.5</v>
+      </c>
+      <c r="AK214">
+        <v>1.38</v>
+      </c>
+      <c r="AL214">
+        <v>1.22</v>
+      </c>
+      <c r="AM214">
+        <v>1.62</v>
+      </c>
+      <c r="AN214">
+        <v>1.6</v>
+      </c>
+      <c r="AO214">
+        <v>1.7</v>
+      </c>
+      <c r="AP214">
+        <v>1.73</v>
+      </c>
+      <c r="AQ214">
+        <v>1.55</v>
+      </c>
+      <c r="AR214">
+        <v>1.73</v>
+      </c>
+      <c r="AS214">
+        <v>1.22</v>
+      </c>
+      <c r="AT214">
+        <v>2.95</v>
+      </c>
+      <c r="AU214">
+        <v>6</v>
+      </c>
+      <c r="AV214">
+        <v>6</v>
+      </c>
+      <c r="AW214">
+        <v>8</v>
+      </c>
+      <c r="AX214">
+        <v>8</v>
+      </c>
+      <c r="AY214">
+        <v>14</v>
+      </c>
+      <c r="AZ214">
+        <v>14</v>
+      </c>
+      <c r="BA214">
+        <v>3</v>
+      </c>
+      <c r="BB214">
+        <v>4</v>
+      </c>
+      <c r="BC214">
+        <v>7</v>
+      </c>
+      <c r="BD214">
+        <v>1.9</v>
+      </c>
+      <c r="BE214">
+        <v>6.5</v>
+      </c>
+      <c r="BF214">
+        <v>2.08</v>
+      </c>
+      <c r="BG214">
+        <v>1.29</v>
+      </c>
+      <c r="BH214">
+        <v>3.2</v>
+      </c>
+      <c r="BI214">
+        <v>1.49</v>
+      </c>
+      <c r="BJ214">
+        <v>2.4</v>
+      </c>
+      <c r="BK214">
+        <v>1.79</v>
+      </c>
+      <c r="BL214">
+        <v>1.9</v>
+      </c>
+      <c r="BM214">
+        <v>2.23</v>
+      </c>
+      <c r="BN214">
+        <v>1.56</v>
+      </c>
+      <c r="BO214">
+        <v>2.85</v>
+      </c>
+      <c r="BP214">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,9 @@
     <t>['3', '19', '31', '40', '56']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1052,6 +1055,9 @@
   </si>
   <si>
     <t>['30', '77']</t>
+  </si>
+  <si>
+    <t>['61', '76']</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1875,7 +1881,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1953,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3">
         <v>1.45</v>
@@ -2081,7 +2087,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2287,7 +2293,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2493,7 +2499,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2699,7 +2705,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2905,7 +2911,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3111,7 +3117,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3523,7 +3529,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3935,7 +3941,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4016,7 +4022,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4553,7 +4559,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5377,7 +5383,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6073,7 +6079,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ23">
         <v>1.45</v>
@@ -6407,7 +6413,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6613,7 +6619,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6819,7 +6825,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7231,7 +7237,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7643,7 +7649,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7930,7 +7936,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ32">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8261,7 +8267,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8467,7 +8473,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9085,7 +9091,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9291,7 +9297,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9703,7 +9709,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9990,7 +9996,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ42">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -10321,7 +10327,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10527,7 +10533,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10733,7 +10739,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10939,7 +10945,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11145,7 +11151,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11557,7 +11563,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11763,7 +11769,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11969,7 +11975,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12047,7 +12053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -12793,7 +12799,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -12871,7 +12877,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ56">
         <v>0.82</v>
@@ -13205,7 +13211,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13411,7 +13417,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13823,7 +13829,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14029,7 +14035,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14235,7 +14241,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14853,7 +14859,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15265,7 +15271,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15471,7 +15477,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15552,7 +15558,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15677,7 +15683,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15883,7 +15889,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16089,7 +16095,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16295,7 +16301,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16501,7 +16507,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16707,7 +16713,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17325,7 +17331,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17531,7 +17537,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17943,7 +17949,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18355,7 +18361,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18561,7 +18567,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19179,7 +19185,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19260,7 +19266,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ87">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -19463,7 +19469,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ88">
         <v>0.64</v>
@@ -19797,7 +19803,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20209,7 +20215,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20621,7 +20627,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20827,7 +20833,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21033,7 +21039,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21239,7 +21245,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21651,7 +21657,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22063,7 +22069,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22269,7 +22275,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22681,7 +22687,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23093,7 +23099,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23380,7 +23386,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -23583,7 +23589,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>0.5</v>
@@ -23917,7 +23923,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24123,7 +24129,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24329,7 +24335,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24741,7 +24747,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24822,7 +24828,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ114">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -24947,7 +24953,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25153,7 +25159,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25359,7 +25365,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25565,7 +25571,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25771,7 +25777,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25977,7 +25983,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26055,7 +26061,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26183,7 +26189,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26389,7 +26395,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26595,7 +26601,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26801,7 +26807,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27007,7 +27013,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27419,7 +27425,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27625,7 +27631,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28037,7 +28043,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28243,7 +28249,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28655,7 +28661,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29273,7 +29279,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29351,7 +29357,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ136">
         <v>0.82</v>
@@ -29560,7 +29566,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ137">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -30715,7 +30721,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30921,7 +30927,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31127,7 +31133,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31333,7 +31339,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31539,7 +31545,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31745,7 +31751,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32157,7 +32163,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32238,7 +32244,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32363,7 +32369,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32775,7 +32781,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32981,7 +32987,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33187,7 +33193,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33471,7 +33477,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -34217,7 +34223,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34629,7 +34635,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35247,7 +35253,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35453,7 +35459,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35659,7 +35665,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35865,7 +35871,7 @@
         <v>92</v>
       </c>
       <c r="P168" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -36071,7 +36077,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36277,7 +36283,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36483,7 +36489,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36895,7 +36901,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37101,7 +37107,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37719,7 +37725,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37925,7 +37931,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38003,7 +38009,7 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ178">
         <v>1.42</v>
@@ -38337,7 +38343,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38418,7 +38424,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ180">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -38543,7 +38549,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39161,7 +39167,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39367,7 +39373,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39573,7 +39579,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40191,7 +40197,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40603,7 +40609,7 @@
         <v>220</v>
       </c>
       <c r="P191" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40809,7 +40815,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41015,7 +41021,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41221,7 +41227,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41427,7 +41433,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41508,7 +41514,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ195">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -41633,7 +41639,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41711,7 +41717,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ196">
         <v>1.55</v>
@@ -42045,7 +42051,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42251,7 +42257,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42663,7 +42669,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42869,7 +42875,7 @@
         <v>140</v>
       </c>
       <c r="P202" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43693,7 +43699,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43899,7 +43905,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44105,7 +44111,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q208">
         <v>1.93</v>
@@ -44311,7 +44317,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q209">
         <v>2.2</v>
@@ -44929,7 +44935,7 @@
         <v>93</v>
       </c>
       <c r="P212" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q212">
         <v>4.2</v>
@@ -45498,6 +45504,212 @@
       </c>
       <c r="BP214">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7465631</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45676.53125</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>71</v>
+      </c>
+      <c r="H215" t="s">
+        <v>70</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215" t="s">
+        <v>235</v>
+      </c>
+      <c r="P215" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q215">
+        <v>2.15</v>
+      </c>
+      <c r="R215">
+        <v>2.35</v>
+      </c>
+      <c r="S215">
+        <v>4.33</v>
+      </c>
+      <c r="T215">
+        <v>1.28</v>
+      </c>
+      <c r="U215">
+        <v>3.3</v>
+      </c>
+      <c r="V215">
+        <v>2.38</v>
+      </c>
+      <c r="W215">
+        <v>1.53</v>
+      </c>
+      <c r="X215">
+        <v>5.45</v>
+      </c>
+      <c r="Y215">
+        <v>1.13</v>
+      </c>
+      <c r="Z215">
+        <v>1.65</v>
+      </c>
+      <c r="AA215">
+        <v>4</v>
+      </c>
+      <c r="AB215">
+        <v>4.5</v>
+      </c>
+      <c r="AC215">
+        <v>1.03</v>
+      </c>
+      <c r="AD215">
+        <v>11</v>
+      </c>
+      <c r="AE215">
+        <v>1.2</v>
+      </c>
+      <c r="AF215">
+        <v>4.5</v>
+      </c>
+      <c r="AG215">
+        <v>1.62</v>
+      </c>
+      <c r="AH215">
+        <v>2.25</v>
+      </c>
+      <c r="AI215">
+        <v>1.62</v>
+      </c>
+      <c r="AJ215">
+        <v>2.1</v>
+      </c>
+      <c r="AK215">
+        <v>1.18</v>
+      </c>
+      <c r="AL215">
+        <v>1.18</v>
+      </c>
+      <c r="AM215">
+        <v>2.15</v>
+      </c>
+      <c r="AN215">
+        <v>1.18</v>
+      </c>
+      <c r="AO215">
+        <v>1.55</v>
+      </c>
+      <c r="AP215">
+        <v>1.08</v>
+      </c>
+      <c r="AQ215">
+        <v>1.67</v>
+      </c>
+      <c r="AR215">
+        <v>1.65</v>
+      </c>
+      <c r="AS215">
+        <v>1.19</v>
+      </c>
+      <c r="AT215">
+        <v>2.84</v>
+      </c>
+      <c r="AU215">
+        <v>5</v>
+      </c>
+      <c r="AV215">
+        <v>10</v>
+      </c>
+      <c r="AW215">
+        <v>10</v>
+      </c>
+      <c r="AX215">
+        <v>5</v>
+      </c>
+      <c r="AY215">
+        <v>15</v>
+      </c>
+      <c r="AZ215">
+        <v>15</v>
+      </c>
+      <c r="BA215">
+        <v>3</v>
+      </c>
+      <c r="BB215">
+        <v>8</v>
+      </c>
+      <c r="BC215">
+        <v>11</v>
+      </c>
+      <c r="BD215">
+        <v>1.5</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>2.8</v>
+      </c>
+      <c r="BG215">
+        <v>1.25</v>
+      </c>
+      <c r="BH215">
+        <v>3.45</v>
+      </c>
+      <c r="BI215">
+        <v>1.44</v>
+      </c>
+      <c r="BJ215">
+        <v>2.55</v>
+      </c>
+      <c r="BK215">
+        <v>1.72</v>
+      </c>
+      <c r="BL215">
+        <v>1.98</v>
+      </c>
+      <c r="BM215">
+        <v>2.1</v>
+      </c>
+      <c r="BN215">
+        <v>1.65</v>
+      </c>
+      <c r="BO215">
+        <v>2.65</v>
+      </c>
+      <c r="BP215">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,22 +706,25 @@
     <t>['58', '66']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
     <t>['17', '56', '67']</t>
   </si>
   <si>
-    <t>['13']</t>
+    <t>['78']</t>
   </si>
   <si>
     <t>['5', '43', '45', '58']</t>
-  </si>
-  <si>
-    <t>['78']</t>
   </si>
   <si>
     <t>['3', '19', '31', '40', '56']</t>
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['17', '28', '55', '90+5']</t>
   </si>
   <si>
     <t>['5', '18']</t>
@@ -1058,6 +1061,9 @@
   </si>
   <si>
     <t>['61', '76']</t>
+  </si>
+  <si>
+    <t>['86']</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1881,7 +1887,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2087,7 +2093,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2293,7 +2299,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2374,7 +2380,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ5">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2499,7 +2505,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2705,7 +2711,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2911,7 +2917,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3117,7 +3123,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3529,7 +3535,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3941,7 +3947,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4225,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ14">
         <v>0.5</v>
@@ -4559,7 +4565,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4637,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ16">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5383,7 +5389,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5667,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ21">
         <v>0.64</v>
@@ -5876,7 +5882,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6413,7 +6419,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6619,7 +6625,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6825,7 +6831,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7237,7 +7243,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7649,7 +7655,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8267,7 +8273,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8348,7 +8354,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ34">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR34">
         <v>1.12</v>
@@ -8473,7 +8479,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8551,7 +8557,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ35">
         <v>2.11</v>
@@ -8966,7 +8972,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ37">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9091,7 +9097,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9297,7 +9303,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9375,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
         <v>1.55</v>
@@ -9709,7 +9715,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9787,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10327,7 +10333,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10533,7 +10539,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10739,7 +10745,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10820,7 +10826,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>1.3</v>
@@ -10945,7 +10951,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11151,7 +11157,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11563,7 +11569,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11769,7 +11775,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11975,7 +11981,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12799,7 +12805,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13211,7 +13217,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13289,7 +13295,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ58">
         <v>1.55</v>
@@ -13417,7 +13423,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13829,7 +13835,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -13907,7 +13913,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -14035,7 +14041,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14116,7 +14122,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ62">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR62">
         <v>1.68</v>
@@ -14241,7 +14247,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14859,7 +14865,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15143,7 +15149,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ67">
         <v>0.64</v>
@@ -15271,7 +15277,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15477,7 +15483,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15683,7 +15689,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15889,7 +15895,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -15967,10 +15973,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16095,7 +16101,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16301,7 +16307,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16507,7 +16513,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16713,7 +16719,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17331,7 +17337,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17537,7 +17543,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17821,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ80">
         <v>1.45</v>
@@ -17949,7 +17955,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18236,7 +18242,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ82">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18361,7 +18367,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18567,7 +18573,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18851,7 +18857,7 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ85">
         <v>1.42</v>
@@ -19057,7 +19063,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19185,7 +19191,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19391,7 +19397,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q88">
         <v>2.1</v>
@@ -19678,7 +19684,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ89">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>1.66</v>
@@ -19803,7 +19809,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20215,7 +20221,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20627,7 +20633,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20833,7 +20839,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21039,7 +21045,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21245,7 +21251,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21529,7 +21535,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ98">
         <v>0.5600000000000001</v>
@@ -21657,7 +21663,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22069,7 +22075,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22275,7 +22281,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22356,7 +22362,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.75</v>
@@ -22687,7 +22693,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22971,7 +22977,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105">
         <v>1.11</v>
@@ -23099,7 +23105,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23795,7 +23801,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ109">
         <v>1.27</v>
@@ -23923,7 +23929,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24129,7 +24135,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24335,7 +24341,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24747,7 +24753,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24953,7 +24959,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25031,7 +25037,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ115">
         <v>0.82</v>
@@ -25159,7 +25165,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25365,7 +25371,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25446,7 +25452,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ117">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25571,7 +25577,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25777,7 +25783,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25858,7 +25864,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ119">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -25983,7 +25989,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26189,7 +26195,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26395,7 +26401,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26476,7 +26482,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ122">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26601,7 +26607,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26679,7 +26685,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>1.3</v>
@@ -26807,7 +26813,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27013,7 +27019,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27425,7 +27431,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27631,7 +27637,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28043,7 +28049,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28121,7 +28127,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ130">
         <v>0.64</v>
@@ -28249,7 +28255,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28661,7 +28667,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29154,7 +29160,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ135">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR135">
         <v>1.75</v>
@@ -29279,7 +29285,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30181,7 +30187,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30721,7 +30727,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30927,7 +30933,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31133,7 +31139,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31339,7 +31345,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31545,7 +31551,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31626,7 +31632,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ147">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -31751,7 +31757,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31829,7 +31835,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ148">
         <v>1.33</v>
@@ -32035,7 +32041,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32163,7 +32169,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32369,7 +32375,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32781,7 +32787,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32987,7 +32993,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33193,7 +33199,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34095,7 +34101,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ159">
         <v>0.82</v>
@@ -34223,7 +34229,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34507,7 +34513,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ161">
         <v>1.42</v>
@@ -34635,7 +34641,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35128,7 +35134,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ164">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35253,7 +35259,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35331,7 +35337,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ165">
         <v>1.73</v>
@@ -35459,7 +35465,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35540,7 +35546,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ166">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -35665,7 +35671,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35871,7 +35877,7 @@
         <v>92</v>
       </c>
       <c r="P168" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -36077,7 +36083,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36283,7 +36289,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36489,7 +36495,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36901,7 +36907,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37107,7 +37113,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37725,7 +37731,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37931,7 +37937,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38215,7 +38221,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38343,7 +38349,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38421,7 +38427,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ180">
         <v>1.67</v>
@@ -38549,7 +38555,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39039,7 +39045,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ183">
         <v>1.45</v>
@@ -39167,7 +39173,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39373,7 +39379,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39579,7 +39585,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39660,7 +39666,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ186">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40197,7 +40203,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40484,7 +40490,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR190">
         <v>1.73</v>
@@ -40609,7 +40615,7 @@
         <v>220</v>
       </c>
       <c r="P191" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40815,7 +40821,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -40893,7 +40899,7 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ192">
         <v>1.45</v>
@@ -41021,7 +41027,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41227,7 +41233,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41433,7 +41439,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41639,7 +41645,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42051,7 +42057,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42257,7 +42263,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42669,7 +42675,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42747,7 +42753,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ201">
         <v>1.33</v>
@@ -42833,7 +42839,7 @@
         <v>201</v>
       </c>
       <c r="B202">
-        <v>7465620</v>
+        <v>7465613</v>
       </c>
       <c r="C202" t="s">
         <v>68</v>
@@ -42848,190 +42854,190 @@
         <v>21</v>
       </c>
       <c r="G202" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H202" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>144</v>
+      </c>
+      <c r="P202" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q202">
         <v>2</v>
       </c>
-      <c r="K202">
-        <v>3</v>
-      </c>
-      <c r="L202">
-        <v>1</v>
-      </c>
-      <c r="M202">
-        <v>3</v>
-      </c>
-      <c r="N202">
-        <v>4</v>
-      </c>
-      <c r="O202" t="s">
-        <v>140</v>
-      </c>
-      <c r="P202" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q202">
+      <c r="R202">
+        <v>2.6</v>
+      </c>
+      <c r="S202">
+        <v>5</v>
+      </c>
+      <c r="T202">
+        <v>1.25</v>
+      </c>
+      <c r="U202">
         <v>3.75</v>
       </c>
-      <c r="R202">
-        <v>2.4</v>
-      </c>
-      <c r="S202">
-        <v>2.5</v>
-      </c>
-      <c r="T202">
-        <v>1.29</v>
-      </c>
-      <c r="U202">
-        <v>3.5</v>
-      </c>
       <c r="V202">
+        <v>2.1</v>
+      </c>
+      <c r="W202">
+        <v>1.67</v>
+      </c>
+      <c r="X202">
+        <v>4.5</v>
+      </c>
+      <c r="Y202">
+        <v>1.18</v>
+      </c>
+      <c r="Z202">
+        <v>1.5</v>
+      </c>
+      <c r="AA202">
+        <v>4.2</v>
+      </c>
+      <c r="AB202">
+        <v>5.75</v>
+      </c>
+      <c r="AC202">
+        <v>1.01</v>
+      </c>
+      <c r="AD202">
+        <v>19</v>
+      </c>
+      <c r="AE202">
+        <v>1.12</v>
+      </c>
+      <c r="AF202">
+        <v>6</v>
+      </c>
+      <c r="AG202">
+        <v>1.44</v>
+      </c>
+      <c r="AH202">
+        <v>2.7</v>
+      </c>
+      <c r="AI202">
+        <v>1.53</v>
+      </c>
+      <c r="AJ202">
         <v>2.38</v>
       </c>
-      <c r="W202">
-        <v>1.53</v>
-      </c>
-      <c r="X202">
-        <v>5.5</v>
-      </c>
-      <c r="Y202">
-        <v>1.14</v>
-      </c>
-      <c r="Z202">
-        <v>3.4</v>
-      </c>
-      <c r="AA202">
-        <v>3.8</v>
-      </c>
-      <c r="AB202">
-        <v>1.95</v>
-      </c>
-      <c r="AC202">
-        <v>1.02</v>
-      </c>
-      <c r="AD202">
-        <v>17</v>
-      </c>
-      <c r="AE202">
-        <v>1.17</v>
-      </c>
-      <c r="AF202">
-        <v>5</v>
-      </c>
-      <c r="AG202">
-        <v>1.57</v>
-      </c>
-      <c r="AH202">
-        <v>2.35</v>
-      </c>
-      <c r="AI202">
-        <v>1.5</v>
-      </c>
-      <c r="AJ202">
-        <v>2.5</v>
-      </c>
       <c r="AK202">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="AL202">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AM202">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="AN202">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="AO202">
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="AQ202">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AR202">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AS202">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AT202">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="AU202">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV202">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW202">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX202">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY202">
         <v>9</v>
       </c>
       <c r="AZ202">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA202">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BB202">
         <v>4</v>
       </c>
       <c r="BC202">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD202">
+        <v>1.46</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>3.05</v>
+      </c>
+      <c r="BG202">
+        <v>1.28</v>
+      </c>
+      <c r="BH202">
+        <v>3.3</v>
+      </c>
+      <c r="BI202">
+        <v>1.49</v>
+      </c>
+      <c r="BJ202">
         <v>2.4</v>
       </c>
-      <c r="BE202">
-        <v>6.4</v>
-      </c>
-      <c r="BF202">
-        <v>1.7</v>
-      </c>
-      <c r="BG202">
-        <v>1.3</v>
-      </c>
-      <c r="BH202">
-        <v>3.05</v>
-      </c>
-      <c r="BI202">
-        <v>1.54</v>
-      </c>
-      <c r="BJ202">
-        <v>2.3</v>
-      </c>
       <c r="BK202">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="BL202">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="BM202">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="BN202">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO202">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BP202">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="203" spans="1:68">
@@ -43245,7 +43251,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>7465613</v>
+        <v>7465620</v>
       </c>
       <c r="C204" t="s">
         <v>68</v>
@@ -43260,190 +43266,190 @@
         <v>21</v>
       </c>
       <c r="G204" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H204" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L204">
         <v>1</v>
       </c>
       <c r="M204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N204">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O204" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="Q204">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="R204">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S204">
+        <v>2.5</v>
+      </c>
+      <c r="T204">
+        <v>1.29</v>
+      </c>
+      <c r="U204">
+        <v>3.5</v>
+      </c>
+      <c r="V204">
+        <v>2.38</v>
+      </c>
+      <c r="W204">
+        <v>1.53</v>
+      </c>
+      <c r="X204">
+        <v>5.5</v>
+      </c>
+      <c r="Y204">
+        <v>1.14</v>
+      </c>
+      <c r="Z204">
+        <v>3.4</v>
+      </c>
+      <c r="AA204">
+        <v>3.8</v>
+      </c>
+      <c r="AB204">
+        <v>1.95</v>
+      </c>
+      <c r="AC204">
+        <v>1.02</v>
+      </c>
+      <c r="AD204">
+        <v>17</v>
+      </c>
+      <c r="AE204">
+        <v>1.17</v>
+      </c>
+      <c r="AF204">
         <v>5</v>
       </c>
-      <c r="T204">
-        <v>1.25</v>
-      </c>
-      <c r="U204">
-        <v>3.75</v>
-      </c>
-      <c r="V204">
-        <v>2.1</v>
-      </c>
-      <c r="W204">
-        <v>1.67</v>
-      </c>
-      <c r="X204">
-        <v>4.5</v>
-      </c>
-      <c r="Y204">
-        <v>1.18</v>
-      </c>
-      <c r="Z204">
+      <c r="AG204">
+        <v>1.57</v>
+      </c>
+      <c r="AH204">
+        <v>2.35</v>
+      </c>
+      <c r="AI204">
         <v>1.5</v>
       </c>
-      <c r="AA204">
-        <v>4.2</v>
-      </c>
-      <c r="AB204">
-        <v>5.75</v>
-      </c>
-      <c r="AC204">
-        <v>1.01</v>
-      </c>
-      <c r="AD204">
-        <v>19</v>
-      </c>
-      <c r="AE204">
-        <v>1.12</v>
-      </c>
-      <c r="AF204">
-        <v>6</v>
-      </c>
-      <c r="AG204">
-        <v>1.44</v>
-      </c>
-      <c r="AH204">
-        <v>2.7</v>
-      </c>
-      <c r="AI204">
-        <v>1.53</v>
-      </c>
       <c r="AJ204">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK204">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL204">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AM204">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="AN204">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="AO204">
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="AQ204">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AR204">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AS204">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AT204">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AU204">
+        <v>3</v>
+      </c>
+      <c r="AV204">
+        <v>6</v>
+      </c>
+      <c r="AW204">
+        <v>3</v>
+      </c>
+      <c r="AX204">
         <v>4</v>
-      </c>
-      <c r="AV204">
-        <v>2</v>
-      </c>
-      <c r="AW204">
-        <v>4</v>
-      </c>
-      <c r="AX204">
-        <v>5</v>
       </c>
       <c r="AY204">
         <v>9</v>
       </c>
       <c r="AZ204">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA204">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BB204">
         <v>4</v>
       </c>
       <c r="BC204">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD204">
-        <v>1.46</v>
+        <v>2.4</v>
       </c>
       <c r="BE204">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF204">
+        <v>1.7</v>
+      </c>
+      <c r="BG204">
+        <v>1.3</v>
+      </c>
+      <c r="BH204">
         <v>3.05</v>
       </c>
-      <c r="BG204">
-        <v>1.28</v>
-      </c>
-      <c r="BH204">
-        <v>3.3</v>
-      </c>
       <c r="BI204">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="BJ204">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK204">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="BL204">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BM204">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="BN204">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO204">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BP204">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="205" spans="1:68">
@@ -43574,7 +43580,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ205">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR205">
         <v>1.65</v>
@@ -43699,7 +43705,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43905,7 +43911,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44069,7 +44075,7 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>7465623</v>
+        <v>7465625</v>
       </c>
       <c r="C208" t="s">
         <v>68</v>
@@ -44084,10 +44090,10 @@
         <v>22</v>
       </c>
       <c r="G208" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H208" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I208">
         <v>1</v>
@@ -44099,175 +44105,175 @@
         <v>1</v>
       </c>
       <c r="L208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M208">
         <v>1</v>
       </c>
       <c r="N208">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O208" t="s">
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="Q208">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="R208">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S208">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="T208">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U208">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="V208">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W208">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X208">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Y208">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z208">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AA208">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AB208">
-        <v>6.25</v>
+        <v>4.32</v>
       </c>
       <c r="AC208">
         <v>1.01</v>
       </c>
       <c r="AD208">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE208">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF208">
+        <v>6.5</v>
+      </c>
+      <c r="AG208">
+        <v>1.4</v>
+      </c>
+      <c r="AH208">
+        <v>2.88</v>
+      </c>
+      <c r="AI208">
+        <v>1.44</v>
+      </c>
+      <c r="AJ208">
+        <v>2.63</v>
+      </c>
+      <c r="AK208">
+        <v>1.22</v>
+      </c>
+      <c r="AL208">
+        <v>1.2</v>
+      </c>
+      <c r="AM208">
+        <v>2.1</v>
+      </c>
+      <c r="AN208">
+        <v>2</v>
+      </c>
+      <c r="AO208">
+        <v>1.3</v>
+      </c>
+      <c r="AP208">
+        <v>1.91</v>
+      </c>
+      <c r="AQ208">
+        <v>1.27</v>
+      </c>
+      <c r="AR208">
+        <v>1.87</v>
+      </c>
+      <c r="AS208">
+        <v>1.31</v>
+      </c>
+      <c r="AT208">
+        <v>3.18</v>
+      </c>
+      <c r="AU208">
         <v>5</v>
-      </c>
-      <c r="AG208">
-        <v>1.5</v>
-      </c>
-      <c r="AH208">
-        <v>2.5</v>
-      </c>
-      <c r="AI208">
-        <v>1.6</v>
-      </c>
-      <c r="AJ208">
-        <v>2.15</v>
-      </c>
-      <c r="AK208">
-        <v>1.11</v>
-      </c>
-      <c r="AL208">
-        <v>1.15</v>
-      </c>
-      <c r="AM208">
-        <v>2.6</v>
-      </c>
-      <c r="AN208">
-        <v>1.91</v>
-      </c>
-      <c r="AO208">
-        <v>1.6</v>
-      </c>
-      <c r="AP208">
-        <v>2</v>
-      </c>
-      <c r="AQ208">
-        <v>1.45</v>
-      </c>
-      <c r="AR208">
-        <v>1.86</v>
-      </c>
-      <c r="AS208">
-        <v>1.29</v>
-      </c>
-      <c r="AT208">
-        <v>3.15</v>
-      </c>
-      <c r="AU208">
-        <v>7</v>
       </c>
       <c r="AV208">
         <v>7</v>
       </c>
       <c r="AW208">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX208">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY208">
+        <v>10</v>
+      </c>
+      <c r="AZ208">
+        <v>14</v>
+      </c>
+      <c r="BA208">
+        <v>5</v>
+      </c>
+      <c r="BB208">
+        <v>7</v>
+      </c>
+      <c r="BC208">
         <v>12</v>
       </c>
-      <c r="AZ208">
-        <v>18</v>
-      </c>
-      <c r="BA208">
-        <v>2</v>
-      </c>
-      <c r="BB208">
-        <v>4</v>
-      </c>
-      <c r="BC208">
-        <v>6</v>
-      </c>
       <c r="BD208">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BE208">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BF208">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="BG208">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BH208">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BI208">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="BJ208">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BK208">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="BL208">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="BM208">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="BN208">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BO208">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="BP208">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="209" spans="1:68">
@@ -44275,7 +44281,7 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>7465625</v>
+        <v>7465623</v>
       </c>
       <c r="C209" t="s">
         <v>68</v>
@@ -44290,10 +44296,10 @@
         <v>22</v>
       </c>
       <c r="G209" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H209" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I209">
         <v>1</v>
@@ -44305,175 +44311,175 @@
         <v>1</v>
       </c>
       <c r="L209">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M209">
         <v>1</v>
       </c>
       <c r="N209">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O209" t="s">
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="Q209">
+        <v>1.93</v>
+      </c>
+      <c r="R209">
+        <v>2.45</v>
+      </c>
+      <c r="S209">
+        <v>5.25</v>
+      </c>
+      <c r="T209">
+        <v>1.25</v>
+      </c>
+      <c r="U209">
+        <v>3.45</v>
+      </c>
+      <c r="V209">
         <v>2.2</v>
       </c>
-      <c r="R209">
-        <v>2.6</v>
-      </c>
-      <c r="S209">
-        <v>4.33</v>
-      </c>
-      <c r="T209">
-        <v>1.22</v>
-      </c>
-      <c r="U209">
-        <v>4</v>
-      </c>
-      <c r="V209">
-        <v>2.1</v>
-      </c>
       <c r="W209">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="X209">
+        <v>4.75</v>
+      </c>
+      <c r="Y209">
+        <v>1.16</v>
+      </c>
+      <c r="Z209">
+        <v>1.45</v>
+      </c>
+      <c r="AA209">
         <v>4.5</v>
       </c>
-      <c r="Y209">
-        <v>1.18</v>
-      </c>
-      <c r="Z209">
-        <v>1.65</v>
-      </c>
-      <c r="AA209">
-        <v>4.29</v>
-      </c>
       <c r="AB209">
-        <v>4.32</v>
+        <v>6.25</v>
       </c>
       <c r="AC209">
         <v>1.01</v>
       </c>
       <c r="AD209">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE209">
+        <v>1.17</v>
+      </c>
+      <c r="AF209">
+        <v>5</v>
+      </c>
+      <c r="AG209">
+        <v>1.5</v>
+      </c>
+      <c r="AH209">
+        <v>2.5</v>
+      </c>
+      <c r="AI209">
+        <v>1.6</v>
+      </c>
+      <c r="AJ209">
+        <v>2.15</v>
+      </c>
+      <c r="AK209">
         <v>1.11</v>
       </c>
-      <c r="AF209">
-        <v>6.5</v>
-      </c>
-      <c r="AG209">
-        <v>1.4</v>
-      </c>
-      <c r="AH209">
-        <v>2.88</v>
-      </c>
-      <c r="AI209">
-        <v>1.44</v>
-      </c>
-      <c r="AJ209">
-        <v>2.63</v>
-      </c>
-      <c r="AK209">
-        <v>1.22</v>
-      </c>
       <c r="AL209">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AM209">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN209">
+        <v>1.91</v>
+      </c>
+      <c r="AO209">
+        <v>1.6</v>
+      </c>
+      <c r="AP209">
         <v>2</v>
       </c>
-      <c r="AO209">
-        <v>1.3</v>
-      </c>
-      <c r="AP209">
-        <v>1.91</v>
-      </c>
       <c r="AQ209">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AR209">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AS209">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AT209">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="AU209">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV209">
         <v>7</v>
       </c>
       <c r="AW209">
+        <v>4</v>
+      </c>
+      <c r="AX209">
+        <v>8</v>
+      </c>
+      <c r="AY209">
+        <v>12</v>
+      </c>
+      <c r="AZ209">
+        <v>18</v>
+      </c>
+      <c r="BA209">
         <v>2</v>
       </c>
-      <c r="AX209">
-        <v>1</v>
-      </c>
-      <c r="AY209">
-        <v>10</v>
-      </c>
-      <c r="AZ209">
-        <v>14</v>
-      </c>
-      <c r="BA209">
-        <v>5</v>
-      </c>
       <c r="BB209">
+        <v>4</v>
+      </c>
+      <c r="BC209">
+        <v>6</v>
+      </c>
+      <c r="BD209">
+        <v>1.43</v>
+      </c>
+      <c r="BE209">
         <v>7</v>
       </c>
-      <c r="BC209">
-        <v>12</v>
-      </c>
-      <c r="BD209">
+      <c r="BF209">
+        <v>3.15</v>
+      </c>
+      <c r="BG209">
+        <v>1.32</v>
+      </c>
+      <c r="BH209">
+        <v>3.05</v>
+      </c>
+      <c r="BI209">
         <v>1.55</v>
       </c>
-      <c r="BE209">
-        <v>6.5</v>
-      </c>
-      <c r="BF209">
-        <v>2.7</v>
-      </c>
-      <c r="BG209">
-        <v>1.25</v>
-      </c>
-      <c r="BH209">
-        <v>3.4</v>
-      </c>
-      <c r="BI209">
-        <v>1.45</v>
-      </c>
       <c r="BJ209">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="BK209">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="BL209">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="BM209">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="BN209">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="BO209">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="BP209">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="210" spans="1:68">
@@ -44481,7 +44487,7 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>7465626</v>
+        <v>7465628</v>
       </c>
       <c r="C210" t="s">
         <v>68</v>
@@ -44496,190 +44502,190 @@
         <v>22</v>
       </c>
       <c r="G210" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H210" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I210">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>2</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>93</v>
+      </c>
+      <c r="P210" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q210">
+        <v>4.2</v>
+      </c>
+      <c r="R210">
+        <v>2.25</v>
+      </c>
+      <c r="S210">
+        <v>2.3</v>
+      </c>
+      <c r="T210">
+        <v>1.33</v>
+      </c>
+      <c r="U210">
+        <v>3.1</v>
+      </c>
+      <c r="V210">
+        <v>2.45</v>
+      </c>
+      <c r="W210">
+        <v>1.48</v>
+      </c>
+      <c r="X210">
+        <v>5.45</v>
+      </c>
+      <c r="Y210">
+        <v>1.13</v>
+      </c>
+      <c r="Z210">
         <v>4</v>
       </c>
-      <c r="M210">
-        <v>0</v>
-      </c>
-      <c r="N210">
-        <v>4</v>
-      </c>
-      <c r="O210" t="s">
-        <v>232</v>
-      </c>
-      <c r="P210" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q210">
-        <v>1.83</v>
-      </c>
-      <c r="R210">
+      <c r="AA210">
+        <v>3.75</v>
+      </c>
+      <c r="AB210">
+        <v>1.8</v>
+      </c>
+      <c r="AC210">
+        <v>1.04</v>
+      </c>
+      <c r="AD210">
+        <v>10</v>
+      </c>
+      <c r="AE210">
+        <v>1.22</v>
+      </c>
+      <c r="AF210">
+        <v>4.2</v>
+      </c>
+      <c r="AG210">
+        <v>1.67</v>
+      </c>
+      <c r="AH210">
+        <v>2.15</v>
+      </c>
+      <c r="AI210">
+        <v>1.57</v>
+      </c>
+      <c r="AJ210">
+        <v>2.2</v>
+      </c>
+      <c r="AK210">
+        <v>1.95</v>
+      </c>
+      <c r="AL210">
+        <v>1.2</v>
+      </c>
+      <c r="AM210">
+        <v>1.22</v>
+      </c>
+      <c r="AN210">
+        <v>1.82</v>
+      </c>
+      <c r="AO210">
+        <v>1.18</v>
+      </c>
+      <c r="AP210">
+        <v>1.67</v>
+      </c>
+      <c r="AQ210">
+        <v>1.33</v>
+      </c>
+      <c r="AR210">
+        <v>1.37</v>
+      </c>
+      <c r="AS210">
+        <v>1.68</v>
+      </c>
+      <c r="AT210">
+        <v>3.05</v>
+      </c>
+      <c r="AU210">
+        <v>8</v>
+      </c>
+      <c r="AV210">
+        <v>8</v>
+      </c>
+      <c r="AW210">
+        <v>7</v>
+      </c>
+      <c r="AX210">
+        <v>6</v>
+      </c>
+      <c r="AY210">
+        <v>23</v>
+      </c>
+      <c r="AZ210">
+        <v>21</v>
+      </c>
+      <c r="BA210">
+        <v>9</v>
+      </c>
+      <c r="BB210">
+        <v>7</v>
+      </c>
+      <c r="BC210">
+        <v>16</v>
+      </c>
+      <c r="BD210">
+        <v>2.8</v>
+      </c>
+      <c r="BE210">
+        <v>6.75</v>
+      </c>
+      <c r="BF210">
+        <v>1.53</v>
+      </c>
+      <c r="BG210">
+        <v>1.24</v>
+      </c>
+      <c r="BH210">
+        <v>3.55</v>
+      </c>
+      <c r="BI210">
+        <v>1.44</v>
+      </c>
+      <c r="BJ210">
+        <v>2.55</v>
+      </c>
+      <c r="BK210">
+        <v>1.72</v>
+      </c>
+      <c r="BL210">
+        <v>1.98</v>
+      </c>
+      <c r="BM210">
+        <v>2.12</v>
+      </c>
+      <c r="BN210">
+        <v>1.64</v>
+      </c>
+      <c r="BO210">
         <v>2.65</v>
       </c>
-      <c r="S210">
-        <v>5</v>
-      </c>
-      <c r="T210">
-        <v>1.2</v>
-      </c>
-      <c r="U210">
-        <v>4</v>
-      </c>
-      <c r="V210">
-        <v>1.95</v>
-      </c>
-      <c r="W210">
-        <v>1.75</v>
-      </c>
-      <c r="X210">
-        <v>4.25</v>
-      </c>
-      <c r="Y210">
-        <v>1.2</v>
-      </c>
-      <c r="Z210">
-        <v>1.4</v>
-      </c>
-      <c r="AA210">
-        <v>5</v>
-      </c>
-      <c r="AB210">
-        <v>6.5</v>
-      </c>
-      <c r="AC210">
-        <v>1.01</v>
-      </c>
-      <c r="AD210">
-        <v>23</v>
-      </c>
-      <c r="AE210">
-        <v>1.1</v>
-      </c>
-      <c r="AF210">
-        <v>6.5</v>
-      </c>
-      <c r="AG210">
-        <v>1.38</v>
-      </c>
-      <c r="AH210">
-        <v>3</v>
-      </c>
-      <c r="AI210">
-        <v>1.48</v>
-      </c>
-      <c r="AJ210">
-        <v>2.4</v>
-      </c>
-      <c r="AK210">
-        <v>1.11</v>
-      </c>
-      <c r="AL210">
-        <v>1.12</v>
-      </c>
-      <c r="AM210">
-        <v>2.8</v>
-      </c>
-      <c r="AN210">
-        <v>2.4</v>
-      </c>
-      <c r="AO210">
-        <v>0.9</v>
-      </c>
-      <c r="AP210">
-        <v>2.45</v>
-      </c>
-      <c r="AQ210">
-        <v>0.82</v>
-      </c>
-      <c r="AR210">
-        <v>1.95</v>
-      </c>
-      <c r="AS210">
-        <v>1.4</v>
-      </c>
-      <c r="AT210">
-        <v>3.35</v>
-      </c>
-      <c r="AU210">
-        <v>6</v>
-      </c>
-      <c r="AV210">
-        <v>7</v>
-      </c>
-      <c r="AW210">
-        <v>6</v>
-      </c>
-      <c r="AX210">
-        <v>5</v>
-      </c>
-      <c r="AY210">
-        <v>15</v>
-      </c>
-      <c r="AZ210">
-        <v>17</v>
-      </c>
-      <c r="BA210">
-        <v>2</v>
-      </c>
-      <c r="BB210">
-        <v>13</v>
-      </c>
-      <c r="BC210">
-        <v>15</v>
-      </c>
-      <c r="BD210">
-        <v>1.38</v>
-      </c>
-      <c r="BE210">
-        <v>7.5</v>
-      </c>
-      <c r="BF210">
-        <v>3.4</v>
-      </c>
-      <c r="BG210">
-        <v>1.23</v>
-      </c>
-      <c r="BH210">
-        <v>3.65</v>
-      </c>
-      <c r="BI210">
-        <v>1.42</v>
-      </c>
-      <c r="BJ210">
-        <v>2.65</v>
-      </c>
-      <c r="BK210">
-        <v>1.67</v>
-      </c>
-      <c r="BL210">
-        <v>2.07</v>
-      </c>
-      <c r="BM210">
-        <v>2.02</v>
-      </c>
-      <c r="BN210">
-        <v>1.7</v>
-      </c>
-      <c r="BO210">
-        <v>2.55</v>
-      </c>
       <c r="BP210">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="211" spans="1:68">
@@ -44687,7 +44693,7 @@
         <v>210</v>
       </c>
       <c r="B211">
-        <v>7465627</v>
+        <v>7465629</v>
       </c>
       <c r="C211" t="s">
         <v>68</v>
@@ -44702,19 +44708,19 @@
         <v>22</v>
       </c>
       <c r="G211" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H211" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211">
         <v>0</v>
       </c>
       <c r="K211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L211">
         <v>1</v>
@@ -44726,25 +44732,25 @@
         <v>1</v>
       </c>
       <c r="O211" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="P211" t="s">
         <v>93</v>
       </c>
       <c r="Q211">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
         <v>2.15</v>
       </c>
       <c r="S211">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="T211">
         <v>1.33</v>
       </c>
       <c r="U211">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V211">
         <v>2.4</v>
@@ -44753,19 +44759,19 @@
         <v>1.5</v>
       </c>
       <c r="X211">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Y211">
         <v>1.12</v>
       </c>
       <c r="Z211">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AA211">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB211">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC211">
         <v>1.04</v>
@@ -44786,76 +44792,76 @@
         <v>2.15</v>
       </c>
       <c r="AI211">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ211">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AK211">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AL211">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM211">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AN211">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="AO211">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AP211">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="AQ211">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="AR211">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AS211">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AT211">
-        <v>3.53</v>
+        <v>3.17</v>
       </c>
       <c r="AU211">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV211">
         <v>4</v>
       </c>
       <c r="AW211">
+        <v>6</v>
+      </c>
+      <c r="AX211">
+        <v>4</v>
+      </c>
+      <c r="AY211">
+        <v>12</v>
+      </c>
+      <c r="AZ211">
+        <v>12</v>
+      </c>
+      <c r="BA211">
+        <v>4</v>
+      </c>
+      <c r="BB211">
         <v>7</v>
       </c>
-      <c r="AX211">
-        <v>6</v>
-      </c>
-      <c r="AY211">
-        <v>18</v>
-      </c>
-      <c r="AZ211">
-        <v>15</v>
-      </c>
-      <c r="BA211">
-        <v>2</v>
-      </c>
-      <c r="BB211">
-        <v>6</v>
-      </c>
       <c r="BC211">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD211">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="BE211">
         <v>6.4</v>
       </c>
       <c r="BF211">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="BG211">
         <v>1.34</v>
@@ -44864,16 +44870,16 @@
         <v>2.9</v>
       </c>
       <c r="BI211">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BJ211">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="BK211">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BL211">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BM211">
         <v>2.45</v>
@@ -44882,7 +44888,7 @@
         <v>1.48</v>
       </c>
       <c r="BO211">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP211">
         <v>1.29</v>
@@ -44893,7 +44899,7 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>7465628</v>
+        <v>7465626</v>
       </c>
       <c r="C212" t="s">
         <v>68</v>
@@ -44908,190 +44914,190 @@
         <v>22</v>
       </c>
       <c r="G212" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H212" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I212">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K212">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L212">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>4</v>
+      </c>
+      <c r="O212" t="s">
+        <v>233</v>
+      </c>
+      <c r="P212" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q212">
+        <v>1.83</v>
+      </c>
+      <c r="R212">
+        <v>2.65</v>
+      </c>
+      <c r="S212">
+        <v>5</v>
+      </c>
+      <c r="T212">
+        <v>1.2</v>
+      </c>
+      <c r="U212">
+        <v>4</v>
+      </c>
+      <c r="V212">
+        <v>1.95</v>
+      </c>
+      <c r="W212">
+        <v>1.75</v>
+      </c>
+      <c r="X212">
+        <v>4.25</v>
+      </c>
+      <c r="Y212">
+        <v>1.2</v>
+      </c>
+      <c r="Z212">
+        <v>1.4</v>
+      </c>
+      <c r="AA212">
+        <v>5</v>
+      </c>
+      <c r="AB212">
+        <v>6.5</v>
+      </c>
+      <c r="AC212">
+        <v>1.01</v>
+      </c>
+      <c r="AD212">
+        <v>23</v>
+      </c>
+      <c r="AE212">
+        <v>1.1</v>
+      </c>
+      <c r="AF212">
+        <v>6.5</v>
+      </c>
+      <c r="AG212">
+        <v>1.38</v>
+      </c>
+      <c r="AH212">
+        <v>3</v>
+      </c>
+      <c r="AI212">
+        <v>1.48</v>
+      </c>
+      <c r="AJ212">
+        <v>2.4</v>
+      </c>
+      <c r="AK212">
+        <v>1.11</v>
+      </c>
+      <c r="AL212">
+        <v>1.12</v>
+      </c>
+      <c r="AM212">
+        <v>2.8</v>
+      </c>
+      <c r="AN212">
+        <v>2.4</v>
+      </c>
+      <c r="AO212">
+        <v>0.9</v>
+      </c>
+      <c r="AP212">
+        <v>2.45</v>
+      </c>
+      <c r="AQ212">
+        <v>0.82</v>
+      </c>
+      <c r="AR212">
+        <v>1.95</v>
+      </c>
+      <c r="AS212">
+        <v>1.4</v>
+      </c>
+      <c r="AT212">
+        <v>3.35</v>
+      </c>
+      <c r="AU212">
+        <v>6</v>
+      </c>
+      <c r="AV212">
+        <v>7</v>
+      </c>
+      <c r="AW212">
+        <v>6</v>
+      </c>
+      <c r="AX212">
+        <v>5</v>
+      </c>
+      <c r="AY212">
+        <v>15</v>
+      </c>
+      <c r="AZ212">
+        <v>17</v>
+      </c>
+      <c r="BA212">
         <v>2</v>
       </c>
-      <c r="N212">
-        <v>2</v>
-      </c>
-      <c r="O212" t="s">
-        <v>93</v>
-      </c>
-      <c r="P212" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q212">
-        <v>4.2</v>
-      </c>
-      <c r="R212">
-        <v>2.25</v>
-      </c>
-      <c r="S212">
-        <v>2.3</v>
-      </c>
-      <c r="T212">
-        <v>1.33</v>
-      </c>
-      <c r="U212">
-        <v>3.1</v>
-      </c>
-      <c r="V212">
-        <v>2.45</v>
-      </c>
-      <c r="W212">
-        <v>1.48</v>
-      </c>
-      <c r="X212">
-        <v>5.45</v>
-      </c>
-      <c r="Y212">
-        <v>1.13</v>
-      </c>
-      <c r="Z212">
-        <v>4</v>
-      </c>
-      <c r="AA212">
-        <v>3.75</v>
-      </c>
-      <c r="AB212">
-        <v>1.8</v>
-      </c>
-      <c r="AC212">
-        <v>1.04</v>
-      </c>
-      <c r="AD212">
-        <v>10</v>
-      </c>
-      <c r="AE212">
-        <v>1.22</v>
-      </c>
-      <c r="AF212">
-        <v>4.2</v>
-      </c>
-      <c r="AG212">
+      <c r="BB212">
+        <v>13</v>
+      </c>
+      <c r="BC212">
+        <v>15</v>
+      </c>
+      <c r="BD212">
+        <v>1.38</v>
+      </c>
+      <c r="BE212">
+        <v>7.5</v>
+      </c>
+      <c r="BF212">
+        <v>3.4</v>
+      </c>
+      <c r="BG212">
+        <v>1.23</v>
+      </c>
+      <c r="BH212">
+        <v>3.65</v>
+      </c>
+      <c r="BI212">
+        <v>1.42</v>
+      </c>
+      <c r="BJ212">
+        <v>2.65</v>
+      </c>
+      <c r="BK212">
         <v>1.67</v>
       </c>
-      <c r="AH212">
-        <v>2.15</v>
-      </c>
-      <c r="AI212">
-        <v>1.57</v>
-      </c>
-      <c r="AJ212">
-        <v>2.2</v>
-      </c>
-      <c r="AK212">
-        <v>1.95</v>
-      </c>
-      <c r="AL212">
-        <v>1.2</v>
-      </c>
-      <c r="AM212">
-        <v>1.22</v>
-      </c>
-      <c r="AN212">
-        <v>1.82</v>
-      </c>
-      <c r="AO212">
-        <v>1.18</v>
-      </c>
-      <c r="AP212">
-        <v>1.67</v>
-      </c>
-      <c r="AQ212">
-        <v>1.33</v>
-      </c>
-      <c r="AR212">
-        <v>1.37</v>
-      </c>
-      <c r="AS212">
-        <v>1.68</v>
-      </c>
-      <c r="AT212">
-        <v>3.05</v>
-      </c>
-      <c r="AU212">
-        <v>8</v>
-      </c>
-      <c r="AV212">
-        <v>8</v>
-      </c>
-      <c r="AW212">
-        <v>7</v>
-      </c>
-      <c r="AX212">
-        <v>6</v>
-      </c>
-      <c r="AY212">
-        <v>23</v>
-      </c>
-      <c r="AZ212">
-        <v>21</v>
-      </c>
-      <c r="BA212">
-        <v>9</v>
-      </c>
-      <c r="BB212">
-        <v>7</v>
-      </c>
-      <c r="BC212">
-        <v>16</v>
-      </c>
-      <c r="BD212">
-        <v>2.8</v>
-      </c>
-      <c r="BE212">
-        <v>6.75</v>
-      </c>
-      <c r="BF212">
-        <v>1.53</v>
-      </c>
-      <c r="BG212">
-        <v>1.24</v>
-      </c>
-      <c r="BH212">
-        <v>3.55</v>
-      </c>
-      <c r="BI212">
-        <v>1.44</v>
-      </c>
-      <c r="BJ212">
+      <c r="BL212">
+        <v>2.07</v>
+      </c>
+      <c r="BM212">
+        <v>2.02</v>
+      </c>
+      <c r="BN212">
+        <v>1.7</v>
+      </c>
+      <c r="BO212">
         <v>2.55</v>
       </c>
-      <c r="BK212">
-        <v>1.72</v>
-      </c>
-      <c r="BL212">
-        <v>1.98</v>
-      </c>
-      <c r="BM212">
-        <v>2.12</v>
-      </c>
-      <c r="BN212">
-        <v>1.64</v>
-      </c>
-      <c r="BO212">
-        <v>2.65</v>
-      </c>
       <c r="BP212">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="213" spans="1:68">
@@ -45099,7 +45105,7 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>7465629</v>
+        <v>7465627</v>
       </c>
       <c r="C213" t="s">
         <v>68</v>
@@ -45114,19 +45120,19 @@
         <v>22</v>
       </c>
       <c r="G213" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H213" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213">
         <v>0</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213">
         <v>1</v>
@@ -45138,25 +45144,25 @@
         <v>1</v>
       </c>
       <c r="O213" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="P213" t="s">
         <v>93</v>
       </c>
       <c r="Q213">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R213">
         <v>2.15</v>
       </c>
       <c r="S213">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T213">
         <v>1.33</v>
       </c>
       <c r="U213">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V213">
         <v>2.4</v>
@@ -45165,19 +45171,19 @@
         <v>1.5</v>
       </c>
       <c r="X213">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Y213">
         <v>1.12</v>
       </c>
       <c r="Z213">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AA213">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB213">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC213">
         <v>1.04</v>
@@ -45198,76 +45204,76 @@
         <v>2.15</v>
       </c>
       <c r="AI213">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ213">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AK213">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AL213">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM213">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AN213">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="AO213">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>0.75</v>
+        <v>1.18</v>
       </c>
       <c r="AQ213">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="AR213">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AS213">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AT213">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="AU213">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV213">
         <v>4</v>
       </c>
       <c r="AW213">
+        <v>7</v>
+      </c>
+      <c r="AX213">
         <v>6</v>
       </c>
-      <c r="AX213">
-        <v>4</v>
-      </c>
       <c r="AY213">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ213">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA213">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB213">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC213">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD213">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="BE213">
         <v>6.4</v>
       </c>
       <c r="BF213">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="BG213">
         <v>1.34</v>
@@ -45276,16 +45282,16 @@
         <v>2.9</v>
       </c>
       <c r="BI213">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BJ213">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="BK213">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BL213">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BM213">
         <v>2.45</v>
@@ -45294,7 +45300,7 @@
         <v>1.48</v>
       </c>
       <c r="BO213">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP213">
         <v>1.29</v>
@@ -45553,7 +45559,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45710,6 +45716,624 @@
       </c>
       <c r="BP215">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7465632</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45677.66666666666</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>89</v>
+      </c>
+      <c r="H216" t="s">
+        <v>79</v>
+      </c>
+      <c r="I216">
+        <v>2</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>2</v>
+      </c>
+      <c r="L216">
+        <v>4</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>4</v>
+      </c>
+      <c r="O216" t="s">
+        <v>236</v>
+      </c>
+      <c r="P216" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q216">
+        <v>2.25</v>
+      </c>
+      <c r="R216">
+        <v>2.6</v>
+      </c>
+      <c r="S216">
+        <v>4</v>
+      </c>
+      <c r="T216">
+        <v>1.19</v>
+      </c>
+      <c r="U216">
+        <v>4.25</v>
+      </c>
+      <c r="V216">
+        <v>1.94</v>
+      </c>
+      <c r="W216">
+        <v>1.79</v>
+      </c>
+      <c r="X216">
+        <v>3.95</v>
+      </c>
+      <c r="Y216">
+        <v>1.21</v>
+      </c>
+      <c r="Z216">
+        <v>1.72</v>
+      </c>
+      <c r="AA216">
+        <v>4.06</v>
+      </c>
+      <c r="AB216">
+        <v>4.28</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>26</v>
+      </c>
+      <c r="AE216">
+        <v>1.09</v>
+      </c>
+      <c r="AF216">
+        <v>7</v>
+      </c>
+      <c r="AG216">
+        <v>1.33</v>
+      </c>
+      <c r="AH216">
+        <v>3.2</v>
+      </c>
+      <c r="AI216">
+        <v>1.36</v>
+      </c>
+      <c r="AJ216">
+        <v>3</v>
+      </c>
+      <c r="AK216">
+        <v>1.25</v>
+      </c>
+      <c r="AL216">
+        <v>1.18</v>
+      </c>
+      <c r="AM216">
+        <v>2.1</v>
+      </c>
+      <c r="AN216">
+        <v>1.2</v>
+      </c>
+      <c r="AO216">
+        <v>1.18</v>
+      </c>
+      <c r="AP216">
+        <v>1.36</v>
+      </c>
+      <c r="AQ216">
+        <v>1.08</v>
+      </c>
+      <c r="AR216">
+        <v>1.61</v>
+      </c>
+      <c r="AS216">
+        <v>1.24</v>
+      </c>
+      <c r="AT216">
+        <v>2.85</v>
+      </c>
+      <c r="AU216">
+        <v>11</v>
+      </c>
+      <c r="AV216">
+        <v>3</v>
+      </c>
+      <c r="AW216">
+        <v>9</v>
+      </c>
+      <c r="AX216">
+        <v>6</v>
+      </c>
+      <c r="AY216">
+        <v>20</v>
+      </c>
+      <c r="AZ216">
+        <v>9</v>
+      </c>
+      <c r="BA216">
+        <v>7</v>
+      </c>
+      <c r="BB216">
+        <v>7</v>
+      </c>
+      <c r="BC216">
+        <v>14</v>
+      </c>
+      <c r="BD216">
+        <v>1.3</v>
+      </c>
+      <c r="BE216">
+        <v>8.6</v>
+      </c>
+      <c r="BF216">
+        <v>4.1</v>
+      </c>
+      <c r="BG216">
+        <v>1.22</v>
+      </c>
+      <c r="BH216">
+        <v>3.8</v>
+      </c>
+      <c r="BI216">
+        <v>1.28</v>
+      </c>
+      <c r="BJ216">
+        <v>3.3</v>
+      </c>
+      <c r="BK216">
+        <v>1.52</v>
+      </c>
+      <c r="BL216">
+        <v>2.32</v>
+      </c>
+      <c r="BM216">
+        <v>1.92</v>
+      </c>
+      <c r="BN216">
+        <v>1.78</v>
+      </c>
+      <c r="BO216">
+        <v>2.55</v>
+      </c>
+      <c r="BP216">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7465634</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45677.66666666666</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>84</v>
+      </c>
+      <c r="H217" t="s">
+        <v>77</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>104</v>
+      </c>
+      <c r="P217" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q217">
+        <v>4.5</v>
+      </c>
+      <c r="R217">
+        <v>2.5</v>
+      </c>
+      <c r="S217">
+        <v>2.2</v>
+      </c>
+      <c r="T217">
+        <v>1.26</v>
+      </c>
+      <c r="U217">
+        <v>3.5</v>
+      </c>
+      <c r="V217">
+        <v>2.34</v>
+      </c>
+      <c r="W217">
+        <v>1.54</v>
+      </c>
+      <c r="X217">
+        <v>5.4</v>
+      </c>
+      <c r="Y217">
+        <v>1.12</v>
+      </c>
+      <c r="Z217">
+        <v>4.7</v>
+      </c>
+      <c r="AA217">
+        <v>4.37</v>
+      </c>
+      <c r="AB217">
+        <v>1.61</v>
+      </c>
+      <c r="AC217">
+        <v>1.02</v>
+      </c>
+      <c r="AD217">
+        <v>19</v>
+      </c>
+      <c r="AE217">
+        <v>1.18</v>
+      </c>
+      <c r="AF217">
+        <v>4.75</v>
+      </c>
+      <c r="AG217">
+        <v>1.6</v>
+      </c>
+      <c r="AH217">
+        <v>2.3</v>
+      </c>
+      <c r="AI217">
+        <v>1.62</v>
+      </c>
+      <c r="AJ217">
+        <v>2.25</v>
+      </c>
+      <c r="AK217">
+        <v>2.2</v>
+      </c>
+      <c r="AL217">
+        <v>1.18</v>
+      </c>
+      <c r="AM217">
+        <v>1.2</v>
+      </c>
+      <c r="AN217">
+        <v>0.73</v>
+      </c>
+      <c r="AO217">
+        <v>1</v>
+      </c>
+      <c r="AP217">
+        <v>0.75</v>
+      </c>
+      <c r="AQ217">
+        <v>1</v>
+      </c>
+      <c r="AR217">
+        <v>1.39</v>
+      </c>
+      <c r="AS217">
+        <v>1.79</v>
+      </c>
+      <c r="AT217">
+        <v>3.18</v>
+      </c>
+      <c r="AU217">
+        <v>2</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>12</v>
+      </c>
+      <c r="AX217">
+        <v>6</v>
+      </c>
+      <c r="AY217">
+        <v>14</v>
+      </c>
+      <c r="AZ217">
+        <v>11</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>7</v>
+      </c>
+      <c r="BC217">
+        <v>12</v>
+      </c>
+      <c r="BD217">
+        <v>2.95</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>1.48</v>
+      </c>
+      <c r="BG217">
+        <v>1.3</v>
+      </c>
+      <c r="BH217">
+        <v>3.15</v>
+      </c>
+      <c r="BI217">
+        <v>1.52</v>
+      </c>
+      <c r="BJ217">
+        <v>2.33</v>
+      </c>
+      <c r="BK217">
+        <v>1.85</v>
+      </c>
+      <c r="BL217">
+        <v>1.83</v>
+      </c>
+      <c r="BM217">
+        <v>2.32</v>
+      </c>
+      <c r="BN217">
+        <v>1.53</v>
+      </c>
+      <c r="BO217">
+        <v>2.95</v>
+      </c>
+      <c r="BP217">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7465617</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45677.66666666666</v>
+      </c>
+      <c r="F218">
+        <v>21</v>
+      </c>
+      <c r="G218" t="s">
+        <v>82</v>
+      </c>
+      <c r="H218" t="s">
+        <v>87</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
+        <v>93</v>
+      </c>
+      <c r="P218" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q218">
+        <v>3.1</v>
+      </c>
+      <c r="R218">
+        <v>2.3</v>
+      </c>
+      <c r="S218">
+        <v>3.1</v>
+      </c>
+      <c r="T218">
+        <v>1.33</v>
+      </c>
+      <c r="U218">
+        <v>3.25</v>
+      </c>
+      <c r="V218">
+        <v>2.5</v>
+      </c>
+      <c r="W218">
+        <v>1.5</v>
+      </c>
+      <c r="X218">
+        <v>6.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.11</v>
+      </c>
+      <c r="Z218">
+        <v>2.55</v>
+      </c>
+      <c r="AA218">
+        <v>3.5</v>
+      </c>
+      <c r="AB218">
+        <v>2.55</v>
+      </c>
+      <c r="AC218">
+        <v>1.02</v>
+      </c>
+      <c r="AD218">
+        <v>15</v>
+      </c>
+      <c r="AE218">
+        <v>1.2</v>
+      </c>
+      <c r="AF218">
+        <v>4.33</v>
+      </c>
+      <c r="AG218">
+        <v>1.67</v>
+      </c>
+      <c r="AH218">
+        <v>2.15</v>
+      </c>
+      <c r="AI218">
+        <v>1.53</v>
+      </c>
+      <c r="AJ218">
+        <v>2.38</v>
+      </c>
+      <c r="AK218">
+        <v>1.52</v>
+      </c>
+      <c r="AL218">
+        <v>1.22</v>
+      </c>
+      <c r="AM218">
+        <v>1.53</v>
+      </c>
+      <c r="AN218">
+        <v>1.89</v>
+      </c>
+      <c r="AO218">
+        <v>2.2</v>
+      </c>
+      <c r="AP218">
+        <v>1.7</v>
+      </c>
+      <c r="AQ218">
+        <v>2.27</v>
+      </c>
+      <c r="AR218">
+        <v>1.9</v>
+      </c>
+      <c r="AS218">
+        <v>1.89</v>
+      </c>
+      <c r="AT218">
+        <v>3.79</v>
+      </c>
+      <c r="AU218">
+        <v>9</v>
+      </c>
+      <c r="AV218">
+        <v>7</v>
+      </c>
+      <c r="AW218">
+        <v>10</v>
+      </c>
+      <c r="AX218">
+        <v>11</v>
+      </c>
+      <c r="AY218">
+        <v>19</v>
+      </c>
+      <c r="AZ218">
+        <v>18</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>4</v>
+      </c>
+      <c r="BC218">
+        <v>9</v>
+      </c>
+      <c r="BD218">
+        <v>1.95</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.05</v>
+      </c>
+      <c r="BG218">
+        <v>1.34</v>
+      </c>
+      <c r="BH218">
+        <v>2.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.57</v>
+      </c>
+      <c r="BJ218">
+        <v>2.23</v>
+      </c>
+      <c r="BK218">
+        <v>1.95</v>
+      </c>
+      <c r="BL218">
+        <v>1.74</v>
+      </c>
+      <c r="BM218">
+        <v>2.45</v>
+      </c>
+      <c r="BN218">
+        <v>1.48</v>
+      </c>
+      <c r="BO218">
+        <v>3.15</v>
+      </c>
+      <c r="BP218">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,21 @@
     <t>['17', '28', '55', '90+5']</t>
   </si>
   <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['45+1', '59', '72', '87']</t>
+  </si>
+  <si>
+    <t>['18', '25', '54', '64']</t>
+  </si>
+  <si>
+    <t>['35', '55', '80']</t>
+  </si>
+  <si>
+    <t>['3', '48', '52']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1030,9 +1045,6 @@
     <t>['24', '89']</t>
   </si>
   <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
     <t>['33']</t>
   </si>
   <si>
@@ -1064,6 +1076,12 @@
   </si>
   <si>
     <t>['86']</t>
+  </si>
+  <si>
+    <t>['12', '38']</t>
+  </si>
+  <si>
+    <t>['30', '52', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1759,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ2">
         <v>1.55</v>
@@ -1887,7 +1905,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1968,7 +1986,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ3">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2093,7 +2111,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2174,7 +2192,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2299,7 +2317,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2380,7 +2398,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ5">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2505,7 +2523,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2711,7 +2729,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2789,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2917,7 +2935,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3123,7 +3141,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3201,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9">
         <v>1.73</v>
@@ -3535,7 +3553,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3947,7 +3965,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4231,10 +4249,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4565,7 +4583,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4849,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ17">
         <v>1.27</v>
@@ -5389,7 +5407,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5467,10 +5485,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5676,7 +5694,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5882,7 +5900,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6291,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR24">
         <v>2.49</v>
@@ -6419,7 +6437,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6497,10 +6515,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ25">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6625,7 +6643,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6831,7 +6849,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -6909,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ27">
         <v>0.82</v>
@@ -7115,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ28">
         <v>1.42</v>
@@ -7243,7 +7261,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7530,7 +7548,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ30">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -7655,7 +7673,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7939,7 +7957,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ32">
         <v>1.67</v>
@@ -8273,7 +8291,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8479,7 +8497,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8560,7 +8578,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -8972,7 +8990,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ37">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9097,7 +9115,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9303,7 +9321,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9587,10 +9605,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -9715,7 +9733,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9793,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9999,7 +10017,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ42">
         <v>1.67</v>
@@ -10208,7 +10226,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR43">
         <v>1.9</v>
@@ -10333,7 +10351,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10539,7 +10557,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10620,7 +10638,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ45">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -10745,7 +10763,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10951,7 +10969,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11157,7 +11175,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11441,10 +11459,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ49">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11569,7 +11587,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11647,7 +11665,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ50">
         <v>1.45</v>
@@ -11775,7 +11793,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11981,7 +11999,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12265,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53">
         <v>1.11</v>
@@ -12805,7 +12823,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13092,7 +13110,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13217,7 +13235,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13423,7 +13441,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13707,10 +13725,10 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ60">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -13835,7 +13853,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14041,7 +14059,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14247,7 +14265,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14531,10 +14549,10 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ64">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -14865,7 +14883,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15149,10 +15167,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ67">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR67">
         <v>1.6</v>
@@ -15277,7 +15295,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15355,7 +15373,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ68">
         <v>0.82</v>
@@ -15483,7 +15501,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15689,7 +15707,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15895,7 +15913,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -15976,7 +15994,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16101,7 +16119,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16179,7 +16197,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ72">
         <v>1.3</v>
@@ -16307,7 +16325,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16388,7 +16406,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16513,7 +16531,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16719,7 +16737,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16800,7 +16818,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17003,7 +17021,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -17337,7 +17355,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17415,7 +17433,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ78">
         <v>0.82</v>
@@ -17543,7 +17561,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17624,7 +17642,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ79">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -17830,7 +17848,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ80">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -17955,7 +17973,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18242,7 +18260,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ82">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18367,7 +18385,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18445,7 +18463,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ83">
         <v>1.73</v>
@@ -18573,7 +18591,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18857,7 +18875,7 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ85">
         <v>1.42</v>
@@ -19191,7 +19209,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19478,7 +19496,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR88">
         <v>1.89</v>
@@ -19809,7 +19827,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -19887,7 +19905,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20221,7 +20239,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20633,7 +20651,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20839,7 +20857,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20920,7 +20938,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21045,7 +21063,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21251,7 +21269,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21538,7 +21556,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ98">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21663,7 +21681,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21741,10 +21759,10 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ99">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -21947,7 +21965,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ100">
         <v>0.82</v>
@@ -22075,7 +22093,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22156,7 +22174,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ101">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR101">
         <v>1.83</v>
@@ -22281,7 +22299,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22359,7 +22377,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ102">
         <v>1.08</v>
@@ -22693,7 +22711,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23105,7 +23123,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23598,7 +23616,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -23929,7 +23947,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24135,7 +24153,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24213,7 +24231,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ111">
         <v>1.55</v>
@@ -24341,7 +24359,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24628,7 +24646,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ113">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -24753,7 +24771,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24831,7 +24849,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ114">
         <v>1.67</v>
@@ -24959,7 +24977,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25037,7 +25055,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ115">
         <v>0.82</v>
@@ -25165,7 +25183,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25371,7 +25389,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25449,7 +25467,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ117">
         <v>1.08</v>
@@ -25577,7 +25595,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25783,7 +25801,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25864,7 +25882,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ119">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -25989,7 +26007,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26195,7 +26213,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26401,7 +26419,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26482,7 +26500,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ122">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26607,7 +26625,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26813,7 +26831,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -26891,10 +26909,10 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ124">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -27019,7 +27037,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27097,7 +27115,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ125">
         <v>1.11</v>
@@ -27303,10 +27321,10 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ126">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -27431,7 +27449,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27509,7 +27527,7 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ127">
         <v>1.33</v>
@@ -27637,7 +27655,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28049,7 +28067,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28130,7 +28148,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ130">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28255,7 +28273,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28336,7 +28354,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ131">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28667,7 +28685,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29285,7 +29303,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29981,10 +29999,10 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ139">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30187,7 +30205,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30727,7 +30745,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30805,10 +30823,10 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ143">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR143">
         <v>1.29</v>
@@ -30933,7 +30951,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31014,7 +31032,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ144">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -31139,7 +31157,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31345,7 +31363,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31426,7 +31444,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ146">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31551,7 +31569,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31629,10 +31647,10 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ147">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -31757,7 +31775,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32169,7 +32187,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32375,7 +32393,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32453,7 +32471,7 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
         <v>1.42</v>
@@ -32659,10 +32677,10 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -32787,7 +32805,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32993,7 +33011,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33199,7 +33217,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33280,7 +33298,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33689,7 +33707,7 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ157">
         <v>0.82</v>
@@ -34101,7 +34119,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ159">
         <v>0.82</v>
@@ -34229,7 +34247,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34641,7 +34659,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34722,7 +34740,7 @@
         <v>2</v>
       </c>
       <c r="AQ162">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35131,7 +35149,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ164">
         <v>1.08</v>
@@ -35259,7 +35277,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35337,7 +35355,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ165">
         <v>1.73</v>
@@ -35465,7 +35483,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35546,7 +35564,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ166">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -35671,7 +35689,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35749,7 +35767,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ167">
         <v>1.45</v>
@@ -35877,7 +35895,7 @@
         <v>92</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35958,7 +35976,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -36083,7 +36101,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36161,7 +36179,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ169">
         <v>1.3</v>
@@ -36289,7 +36307,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36367,10 +36385,10 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ170">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -36495,7 +36513,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36576,7 +36594,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ171">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -36782,7 +36800,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ172">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -36907,7 +36925,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37113,7 +37131,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37397,7 +37415,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ175">
         <v>1.27</v>
@@ -37731,7 +37749,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37937,7 +37955,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38349,7 +38367,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38555,7 +38573,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39045,10 +39063,10 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ183">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -39173,7 +39191,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39254,7 +39272,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ184">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39379,7 +39397,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39457,7 +39475,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ185">
         <v>1.3</v>
@@ -39585,7 +39603,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39663,10 +39681,10 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ186">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40078,7 +40096,7 @@
         <v>2</v>
       </c>
       <c r="AQ188">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40203,7 +40221,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40487,7 +40505,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ190">
         <v>1.08</v>
@@ -40615,7 +40633,7 @@
         <v>220</v>
       </c>
       <c r="P191" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40693,10 +40711,10 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ191">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -40821,7 +40839,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41027,7 +41045,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41233,7 +41251,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41439,7 +41457,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41645,7 +41663,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42057,7 +42075,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42135,7 +42153,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42263,7 +42281,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42550,7 +42568,7 @@
         <v>2</v>
       </c>
       <c r="AQ200">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42675,7 +42693,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42962,7 +42980,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ202">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -43168,7 +43186,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ203">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -43293,7 +43311,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43371,7 +43389,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ204">
         <v>1.73</v>
@@ -43705,7 +43723,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43783,7 +43801,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ206">
         <v>1.3</v>
@@ -43911,7 +43929,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44117,7 +44135,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44323,7 +44341,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44529,7 +44547,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -45019,7 +45037,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ212">
         <v>0.82</v>
@@ -45559,7 +45577,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45971,7 +45989,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46177,7 +46195,7 @@
         <v>93</v>
       </c>
       <c r="P218" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q218">
         <v>3.1</v>
@@ -46255,10 +46273,10 @@
         <v>2.2</v>
       </c>
       <c r="AP218">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ218">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AR218">
         <v>1.9</v>
@@ -46334,6 +46352,1242 @@
       </c>
       <c r="BP218">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7467160</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F219">
+        <v>23</v>
+      </c>
+      <c r="G219" t="s">
+        <v>85</v>
+      </c>
+      <c r="H219" t="s">
+        <v>74</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
+        <v>237</v>
+      </c>
+      <c r="P219" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q219">
+        <v>2.25</v>
+      </c>
+      <c r="R219">
+        <v>2.4</v>
+      </c>
+      <c r="S219">
+        <v>4.5</v>
+      </c>
+      <c r="T219">
+        <v>1.29</v>
+      </c>
+      <c r="U219">
+        <v>3.35</v>
+      </c>
+      <c r="V219">
+        <v>2.45</v>
+      </c>
+      <c r="W219">
+        <v>1.49</v>
+      </c>
+      <c r="X219">
+        <v>5.45</v>
+      </c>
+      <c r="Y219">
+        <v>1.12</v>
+      </c>
+      <c r="Z219">
+        <v>1.7</v>
+      </c>
+      <c r="AA219">
+        <v>3.97</v>
+      </c>
+      <c r="AB219">
+        <v>4.55</v>
+      </c>
+      <c r="AC219">
+        <v>1.02</v>
+      </c>
+      <c r="AD219">
+        <v>15</v>
+      </c>
+      <c r="AE219">
+        <v>1.22</v>
+      </c>
+      <c r="AF219">
+        <v>4.33</v>
+      </c>
+      <c r="AG219">
+        <v>1.68</v>
+      </c>
+      <c r="AH219">
+        <v>2.15</v>
+      </c>
+      <c r="AI219">
+        <v>1.68</v>
+      </c>
+      <c r="AJ219">
+        <v>2.15</v>
+      </c>
+      <c r="AK219">
+        <v>1.2</v>
+      </c>
+      <c r="AL219">
+        <v>1.2</v>
+      </c>
+      <c r="AM219">
+        <v>2.15</v>
+      </c>
+      <c r="AN219">
+        <v>1.6</v>
+      </c>
+      <c r="AO219">
+        <v>0.5</v>
+      </c>
+      <c r="AP219">
+        <v>1.73</v>
+      </c>
+      <c r="AQ219">
+        <v>0.45</v>
+      </c>
+      <c r="AR219">
+        <v>1.74</v>
+      </c>
+      <c r="AS219">
+        <v>1.15</v>
+      </c>
+      <c r="AT219">
+        <v>2.89</v>
+      </c>
+      <c r="AU219">
+        <v>6</v>
+      </c>
+      <c r="AV219">
+        <v>0</v>
+      </c>
+      <c r="AW219">
+        <v>9</v>
+      </c>
+      <c r="AX219">
+        <v>5</v>
+      </c>
+      <c r="AY219">
+        <v>15</v>
+      </c>
+      <c r="AZ219">
+        <v>5</v>
+      </c>
+      <c r="BA219">
+        <v>1</v>
+      </c>
+      <c r="BB219">
+        <v>6</v>
+      </c>
+      <c r="BC219">
+        <v>7</v>
+      </c>
+      <c r="BD219">
+        <v>1.53</v>
+      </c>
+      <c r="BE219">
+        <v>7</v>
+      </c>
+      <c r="BF219">
+        <v>2.7</v>
+      </c>
+      <c r="BG219">
+        <v>1.24</v>
+      </c>
+      <c r="BH219">
+        <v>3.65</v>
+      </c>
+      <c r="BI219">
+        <v>1.41</v>
+      </c>
+      <c r="BJ219">
+        <v>2.65</v>
+      </c>
+      <c r="BK219">
+        <v>1.67</v>
+      </c>
+      <c r="BL219">
+        <v>2.07</v>
+      </c>
+      <c r="BM219">
+        <v>2.02</v>
+      </c>
+      <c r="BN219">
+        <v>1.68</v>
+      </c>
+      <c r="BO219">
+        <v>2.55</v>
+      </c>
+      <c r="BP219">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7465635</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F220">
+        <v>23</v>
+      </c>
+      <c r="G220" t="s">
+        <v>77</v>
+      </c>
+      <c r="H220" t="s">
+        <v>71</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>4</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>238</v>
+      </c>
+      <c r="P220" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q220">
+        <v>2.63</v>
+      </c>
+      <c r="R220">
+        <v>2.4</v>
+      </c>
+      <c r="S220">
+        <v>3.5</v>
+      </c>
+      <c r="T220">
+        <v>1.29</v>
+      </c>
+      <c r="U220">
+        <v>3.5</v>
+      </c>
+      <c r="V220">
+        <v>2.25</v>
+      </c>
+      <c r="W220">
+        <v>1.57</v>
+      </c>
+      <c r="X220">
+        <v>5.5</v>
+      </c>
+      <c r="Y220">
+        <v>1.14</v>
+      </c>
+      <c r="Z220">
+        <v>2.11</v>
+      </c>
+      <c r="AA220">
+        <v>3.68</v>
+      </c>
+      <c r="AB220">
+        <v>3.16</v>
+      </c>
+      <c r="AC220">
+        <v>1.02</v>
+      </c>
+      <c r="AD220">
+        <v>13</v>
+      </c>
+      <c r="AE220">
+        <v>1.18</v>
+      </c>
+      <c r="AF220">
+        <v>5</v>
+      </c>
+      <c r="AG220">
+        <v>1.57</v>
+      </c>
+      <c r="AH220">
+        <v>2.35</v>
+      </c>
+      <c r="AI220">
+        <v>1.44</v>
+      </c>
+      <c r="AJ220">
+        <v>2.63</v>
+      </c>
+      <c r="AK220">
+        <v>1.35</v>
+      </c>
+      <c r="AL220">
+        <v>1.27</v>
+      </c>
+      <c r="AM220">
+        <v>1.68</v>
+      </c>
+      <c r="AN220">
+        <v>2.2</v>
+      </c>
+      <c r="AO220">
+        <v>2.11</v>
+      </c>
+      <c r="AP220">
+        <v>2.27</v>
+      </c>
+      <c r="AQ220">
+        <v>1.9</v>
+      </c>
+      <c r="AR220">
+        <v>1.66</v>
+      </c>
+      <c r="AS220">
+        <v>1.76</v>
+      </c>
+      <c r="AT220">
+        <v>3.42</v>
+      </c>
+      <c r="AU220">
+        <v>10</v>
+      </c>
+      <c r="AV220">
+        <v>2</v>
+      </c>
+      <c r="AW220">
+        <v>23</v>
+      </c>
+      <c r="AX220">
+        <v>3</v>
+      </c>
+      <c r="AY220">
+        <v>33</v>
+      </c>
+      <c r="AZ220">
+        <v>5</v>
+      </c>
+      <c r="BA220">
+        <v>12</v>
+      </c>
+      <c r="BB220">
+        <v>4</v>
+      </c>
+      <c r="BC220">
+        <v>16</v>
+      </c>
+      <c r="BD220">
+        <v>1.82</v>
+      </c>
+      <c r="BE220">
+        <v>6.5</v>
+      </c>
+      <c r="BF220">
+        <v>2.18</v>
+      </c>
+      <c r="BG220">
+        <v>1.29</v>
+      </c>
+      <c r="BH220">
+        <v>3.15</v>
+      </c>
+      <c r="BI220">
+        <v>1.5</v>
+      </c>
+      <c r="BJ220">
+        <v>2.38</v>
+      </c>
+      <c r="BK220">
+        <v>1.81</v>
+      </c>
+      <c r="BL220">
+        <v>1.88</v>
+      </c>
+      <c r="BM220">
+        <v>2.23</v>
+      </c>
+      <c r="BN220">
+        <v>1.56</v>
+      </c>
+      <c r="BO220">
+        <v>2.9</v>
+      </c>
+      <c r="BP220">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7465636</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F221">
+        <v>23</v>
+      </c>
+      <c r="G221" t="s">
+        <v>70</v>
+      </c>
+      <c r="H221" t="s">
+        <v>87</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="K221">
+        <v>4</v>
+      </c>
+      <c r="L221">
+        <v>4</v>
+      </c>
+      <c r="M221">
+        <v>2</v>
+      </c>
+      <c r="N221">
+        <v>6</v>
+      </c>
+      <c r="O221" t="s">
+        <v>239</v>
+      </c>
+      <c r="P221" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q221">
+        <v>3.6</v>
+      </c>
+      <c r="R221">
+        <v>2.3</v>
+      </c>
+      <c r="S221">
+        <v>2.75</v>
+      </c>
+      <c r="T221">
+        <v>1.33</v>
+      </c>
+      <c r="U221">
+        <v>3.25</v>
+      </c>
+      <c r="V221">
+        <v>2.63</v>
+      </c>
+      <c r="W221">
+        <v>1.44</v>
+      </c>
+      <c r="X221">
+        <v>6.5</v>
+      </c>
+      <c r="Y221">
+        <v>1.11</v>
+      </c>
+      <c r="Z221">
+        <v>3.19</v>
+      </c>
+      <c r="AA221">
+        <v>3.63</v>
+      </c>
+      <c r="AB221">
+        <v>2.11</v>
+      </c>
+      <c r="AC221">
+        <v>1.03</v>
+      </c>
+      <c r="AD221">
+        <v>13</v>
+      </c>
+      <c r="AE221">
+        <v>1.22</v>
+      </c>
+      <c r="AF221">
+        <v>4</v>
+      </c>
+      <c r="AG221">
+        <v>1.7</v>
+      </c>
+      <c r="AH221">
+        <v>2.1</v>
+      </c>
+      <c r="AI221">
+        <v>1.57</v>
+      </c>
+      <c r="AJ221">
+        <v>2.25</v>
+      </c>
+      <c r="AK221">
+        <v>1.71</v>
+      </c>
+      <c r="AL221">
+        <v>1.27</v>
+      </c>
+      <c r="AM221">
+        <v>1.33</v>
+      </c>
+      <c r="AN221">
+        <v>0.9</v>
+      </c>
+      <c r="AO221">
+        <v>2.27</v>
+      </c>
+      <c r="AP221">
+        <v>1.09</v>
+      </c>
+      <c r="AQ221">
+        <v>2.08</v>
+      </c>
+      <c r="AR221">
+        <v>1.34</v>
+      </c>
+      <c r="AS221">
+        <v>1.9</v>
+      </c>
+      <c r="AT221">
+        <v>3.24</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>6</v>
+      </c>
+      <c r="AW221">
+        <v>6</v>
+      </c>
+      <c r="AX221">
+        <v>6</v>
+      </c>
+      <c r="AY221">
+        <v>11</v>
+      </c>
+      <c r="AZ221">
+        <v>12</v>
+      </c>
+      <c r="BA221">
+        <v>3</v>
+      </c>
+      <c r="BB221">
+        <v>4</v>
+      </c>
+      <c r="BC221">
+        <v>7</v>
+      </c>
+      <c r="BD221">
+        <v>2.38</v>
+      </c>
+      <c r="BE221">
+        <v>6.5</v>
+      </c>
+      <c r="BF221">
+        <v>1.72</v>
+      </c>
+      <c r="BG221">
+        <v>1.26</v>
+      </c>
+      <c r="BH221">
+        <v>3.4</v>
+      </c>
+      <c r="BI221">
+        <v>1.45</v>
+      </c>
+      <c r="BJ221">
+        <v>2.55</v>
+      </c>
+      <c r="BK221">
+        <v>1.72</v>
+      </c>
+      <c r="BL221">
+        <v>1.98</v>
+      </c>
+      <c r="BM221">
+        <v>2.12</v>
+      </c>
+      <c r="BN221">
+        <v>1.63</v>
+      </c>
+      <c r="BO221">
+        <v>2.65</v>
+      </c>
+      <c r="BP221">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7465637</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>88</v>
+      </c>
+      <c r="H222" t="s">
+        <v>73</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>3</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>4</v>
+      </c>
+      <c r="O222" t="s">
+        <v>240</v>
+      </c>
+      <c r="P222" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q222">
+        <v>1.85</v>
+      </c>
+      <c r="R222">
+        <v>2.8</v>
+      </c>
+      <c r="S222">
+        <v>5.5</v>
+      </c>
+      <c r="T222">
+        <v>1.18</v>
+      </c>
+      <c r="U222">
+        <v>4.4</v>
+      </c>
+      <c r="V222">
+        <v>1.94</v>
+      </c>
+      <c r="W222">
+        <v>1.79</v>
+      </c>
+      <c r="X222">
+        <v>3.95</v>
+      </c>
+      <c r="Y222">
+        <v>1.21</v>
+      </c>
+      <c r="Z222">
+        <v>1.41</v>
+      </c>
+      <c r="AA222">
+        <v>5.14</v>
+      </c>
+      <c r="AB222">
+        <v>6.17</v>
+      </c>
+      <c r="AC222">
+        <v>1.01</v>
+      </c>
+      <c r="AD222">
+        <v>23</v>
+      </c>
+      <c r="AE222">
+        <v>1.1</v>
+      </c>
+      <c r="AF222">
+        <v>7</v>
+      </c>
+      <c r="AG222">
+        <v>1.35</v>
+      </c>
+      <c r="AH222">
+        <v>3.1</v>
+      </c>
+      <c r="AI222">
+        <v>1.5</v>
+      </c>
+      <c r="AJ222">
+        <v>2.5</v>
+      </c>
+      <c r="AK222">
+        <v>1.11</v>
+      </c>
+      <c r="AL222">
+        <v>1.12</v>
+      </c>
+      <c r="AM222">
+        <v>2.9</v>
+      </c>
+      <c r="AN222">
+        <v>2.45</v>
+      </c>
+      <c r="AO222">
+        <v>0.64</v>
+      </c>
+      <c r="AP222">
+        <v>2.5</v>
+      </c>
+      <c r="AQ222">
+        <v>0.58</v>
+      </c>
+      <c r="AR222">
+        <v>1.91</v>
+      </c>
+      <c r="AS222">
+        <v>1.26</v>
+      </c>
+      <c r="AT222">
+        <v>3.17</v>
+      </c>
+      <c r="AU222">
+        <v>10</v>
+      </c>
+      <c r="AV222">
+        <v>6</v>
+      </c>
+      <c r="AW222">
+        <v>5</v>
+      </c>
+      <c r="AX222">
+        <v>10</v>
+      </c>
+      <c r="AY222">
+        <v>18</v>
+      </c>
+      <c r="AZ222">
+        <v>24</v>
+      </c>
+      <c r="BA222">
+        <v>4</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>9</v>
+      </c>
+      <c r="BD222">
+        <v>1.42</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
+        <v>3.2</v>
+      </c>
+      <c r="BG222">
+        <v>1.33</v>
+      </c>
+      <c r="BH222">
+        <v>2.95</v>
+      </c>
+      <c r="BI222">
+        <v>1.57</v>
+      </c>
+      <c r="BJ222">
+        <v>2.23</v>
+      </c>
+      <c r="BK222">
+        <v>1.93</v>
+      </c>
+      <c r="BL222">
+        <v>1.77</v>
+      </c>
+      <c r="BM222">
+        <v>2.4</v>
+      </c>
+      <c r="BN222">
+        <v>1.49</v>
+      </c>
+      <c r="BO222">
+        <v>3.15</v>
+      </c>
+      <c r="BP222">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7465638</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F223">
+        <v>23</v>
+      </c>
+      <c r="G223" t="s">
+        <v>82</v>
+      </c>
+      <c r="H223" t="s">
+        <v>84</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>3</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>3</v>
+      </c>
+      <c r="O223" t="s">
+        <v>241</v>
+      </c>
+      <c r="P223" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q223">
+        <v>1.8</v>
+      </c>
+      <c r="R223">
+        <v>2.6</v>
+      </c>
+      <c r="S223">
+        <v>7</v>
+      </c>
+      <c r="T223">
+        <v>1.29</v>
+      </c>
+      <c r="U223">
+        <v>3.5</v>
+      </c>
+      <c r="V223">
+        <v>2.25</v>
+      </c>
+      <c r="W223">
+        <v>1.57</v>
+      </c>
+      <c r="X223">
+        <v>5.5</v>
+      </c>
+      <c r="Y223">
+        <v>1.14</v>
+      </c>
+      <c r="Z223">
+        <v>1.32</v>
+      </c>
+      <c r="AA223">
+        <v>5.28</v>
+      </c>
+      <c r="AB223">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AC223">
+        <v>1.02</v>
+      </c>
+      <c r="AD223">
+        <v>17</v>
+      </c>
+      <c r="AE223">
+        <v>1.18</v>
+      </c>
+      <c r="AF223">
+        <v>4.75</v>
+      </c>
+      <c r="AG223">
+        <v>1.57</v>
+      </c>
+      <c r="AH223">
+        <v>2.35</v>
+      </c>
+      <c r="AI223">
+        <v>1.83</v>
+      </c>
+      <c r="AJ223">
+        <v>1.83</v>
+      </c>
+      <c r="AK223">
+        <v>1.1</v>
+      </c>
+      <c r="AL223">
+        <v>1.16</v>
+      </c>
+      <c r="AM223">
+        <v>2.95</v>
+      </c>
+      <c r="AN223">
+        <v>1.7</v>
+      </c>
+      <c r="AO223">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP223">
+        <v>1.82</v>
+      </c>
+      <c r="AQ223">
+        <v>0.5</v>
+      </c>
+      <c r="AR223">
+        <v>1.93</v>
+      </c>
+      <c r="AS223">
+        <v>1.21</v>
+      </c>
+      <c r="AT223">
+        <v>3.14</v>
+      </c>
+      <c r="AU223">
+        <v>9</v>
+      </c>
+      <c r="AV223">
+        <v>4</v>
+      </c>
+      <c r="AW223">
+        <v>8</v>
+      </c>
+      <c r="AX223">
+        <v>11</v>
+      </c>
+      <c r="AY223">
+        <v>17</v>
+      </c>
+      <c r="AZ223">
+        <v>15</v>
+      </c>
+      <c r="BA223">
+        <v>7</v>
+      </c>
+      <c r="BB223">
+        <v>3</v>
+      </c>
+      <c r="BC223">
+        <v>10</v>
+      </c>
+      <c r="BD223">
+        <v>1.28</v>
+      </c>
+      <c r="BE223">
+        <v>7.5</v>
+      </c>
+      <c r="BF223">
+        <v>3.95</v>
+      </c>
+      <c r="BG223">
+        <v>1.33</v>
+      </c>
+      <c r="BH223">
+        <v>2.95</v>
+      </c>
+      <c r="BI223">
+        <v>1.56</v>
+      </c>
+      <c r="BJ223">
+        <v>2.23</v>
+      </c>
+      <c r="BK223">
+        <v>1.91</v>
+      </c>
+      <c r="BL223">
+        <v>1.78</v>
+      </c>
+      <c r="BM223">
+        <v>2.4</v>
+      </c>
+      <c r="BN223">
+        <v>1.49</v>
+      </c>
+      <c r="BO223">
+        <v>3.15</v>
+      </c>
+      <c r="BP223">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7465639</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F224">
+        <v>23</v>
+      </c>
+      <c r="G224" t="s">
+        <v>75</v>
+      </c>
+      <c r="H224" t="s">
+        <v>86</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>1</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>3</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>93</v>
+      </c>
+      <c r="P224" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q224">
+        <v>3.2</v>
+      </c>
+      <c r="R224">
+        <v>2.4</v>
+      </c>
+      <c r="S224">
+        <v>2.9</v>
+      </c>
+      <c r="T224">
+        <v>1.24</v>
+      </c>
+      <c r="U224">
+        <v>3.7</v>
+      </c>
+      <c r="V224">
+        <v>2.19</v>
+      </c>
+      <c r="W224">
+        <v>1.62</v>
+      </c>
+      <c r="X224">
+        <v>4.7</v>
+      </c>
+      <c r="Y224">
+        <v>1.16</v>
+      </c>
+      <c r="Z224">
+        <v>2.8</v>
+      </c>
+      <c r="AA224">
+        <v>3.68</v>
+      </c>
+      <c r="AB224">
+        <v>2.35</v>
+      </c>
+      <c r="AC224">
+        <v>1.01</v>
+      </c>
+      <c r="AD224">
+        <v>17</v>
+      </c>
+      <c r="AE224">
+        <v>1.15</v>
+      </c>
+      <c r="AF224">
+        <v>5.5</v>
+      </c>
+      <c r="AG224">
+        <v>1.47</v>
+      </c>
+      <c r="AH224">
+        <v>2.65</v>
+      </c>
+      <c r="AI224">
+        <v>1.42</v>
+      </c>
+      <c r="AJ224">
+        <v>2.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.6</v>
+      </c>
+      <c r="AL224">
+        <v>1.22</v>
+      </c>
+      <c r="AM224">
+        <v>1.47</v>
+      </c>
+      <c r="AN224">
+        <v>0.91</v>
+      </c>
+      <c r="AO224">
+        <v>1.45</v>
+      </c>
+      <c r="AP224">
+        <v>0.83</v>
+      </c>
+      <c r="AQ224">
+        <v>1.58</v>
+      </c>
+      <c r="AR224">
+        <v>1.73</v>
+      </c>
+      <c r="AS224">
+        <v>1.29</v>
+      </c>
+      <c r="AT224">
+        <v>3.02</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>11</v>
+      </c>
+      <c r="AX224">
+        <v>1</v>
+      </c>
+      <c r="AY224">
+        <v>16</v>
+      </c>
+      <c r="AZ224">
+        <v>5</v>
+      </c>
+      <c r="BA224">
+        <v>5</v>
+      </c>
+      <c r="BB224">
+        <v>4</v>
+      </c>
+      <c r="BC224">
+        <v>9</v>
+      </c>
+      <c r="BD224">
+        <v>2.2</v>
+      </c>
+      <c r="BE224">
+        <v>6.5</v>
+      </c>
+      <c r="BF224">
+        <v>1.79</v>
+      </c>
+      <c r="BG224">
+        <v>1.2</v>
+      </c>
+      <c r="BH224">
+        <v>3.95</v>
+      </c>
+      <c r="BI224">
+        <v>1.36</v>
+      </c>
+      <c r="BJ224">
+        <v>2.8</v>
+      </c>
+      <c r="BK224">
+        <v>1.58</v>
+      </c>
+      <c r="BL224">
+        <v>2.18</v>
+      </c>
+      <c r="BM224">
+        <v>1.95</v>
+      </c>
+      <c r="BN224">
+        <v>1.75</v>
+      </c>
+      <c r="BO224">
+        <v>2.43</v>
+      </c>
+      <c r="BP224">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
